--- a/ModExample/Defs/excel_data/物品表_养殖_动物.xlsx
+++ b/ModExample/Defs/excel_data/物品表_养殖_动物.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Territory\数值表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CF23ED-5DB1-47F1-B162-F31EF4E135A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A0F7AA-4546-4C23-8A7D-7DA202F36000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29640" yWindow="1695" windowWidth="28830" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="203">
   <si>
     <t>产量</t>
   </si>
@@ -856,6 +856,81 @@
 肉
 熏鱼
 熏肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画Idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画Walk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ody_idle#str</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_walk#str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7,8,9,10</t>
+  </si>
+  <si>
+    <t>11,12,13,14</t>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16,17,18,19,20,21,22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21,22,23,24,25,26,27,28,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,0,0,0,0,0,0,0,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7,8,9,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,12,13,14,15,16,17,18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画图集中的总帧数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>total_frame_count#int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1056,6 +1131,7 @@
     <sheetNames>
       <sheetName val="stuff"/>
       <sheetName val="stuff2"/>
+      <sheetName val="stuff_type_name"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1303,10 +1379,10 @@
         </row>
         <row r="23">
           <cell r="A23">
-            <v>103001</v>
+            <v>102013</v>
           </cell>
           <cell r="B23" t="str">
-            <v>大箱子</v>
+            <v>石桥</v>
           </cell>
           <cell r="C23">
             <v>0</v>
@@ -1314,10 +1390,10 @@
         </row>
         <row r="24">
           <cell r="A24">
-            <v>103002</v>
+            <v>103001</v>
           </cell>
           <cell r="B24" t="str">
-            <v>料堆</v>
+            <v>大箱子</v>
           </cell>
           <cell r="C24">
             <v>0</v>
@@ -1325,10 +1401,10 @@
         </row>
         <row r="25">
           <cell r="A25">
-            <v>103003</v>
+            <v>103002</v>
           </cell>
           <cell r="B25" t="str">
-            <v>货架</v>
+            <v>料堆</v>
           </cell>
           <cell r="C25">
             <v>0</v>
@@ -1336,10 +1412,10 @@
         </row>
         <row r="26">
           <cell r="A26">
-            <v>103004</v>
+            <v>103003</v>
           </cell>
           <cell r="B26" t="str">
-            <v>交易台</v>
+            <v>货架</v>
           </cell>
           <cell r="C26">
             <v>0</v>
@@ -1347,10 +1423,10 @@
         </row>
         <row r="27">
           <cell r="A27">
-            <v>103005</v>
+            <v>103004</v>
           </cell>
           <cell r="B27" t="str">
-            <v>边贸口岸</v>
+            <v>交易台</v>
           </cell>
           <cell r="C27">
             <v>0</v>
@@ -1358,10 +1434,10 @@
         </row>
         <row r="28">
           <cell r="A28">
-            <v>103006</v>
+            <v>103005</v>
           </cell>
           <cell r="B28" t="str">
-            <v>路标</v>
+            <v>边贸口岸</v>
           </cell>
           <cell r="C28">
             <v>0</v>
@@ -1369,10 +1445,10 @@
         </row>
         <row r="29">
           <cell r="A29">
-            <v>103007</v>
+            <v>103006</v>
           </cell>
           <cell r="B29" t="str">
-            <v>冰窖</v>
+            <v>路标</v>
           </cell>
           <cell r="C29">
             <v>0</v>
@@ -1380,10 +1456,10 @@
         </row>
         <row r="30">
           <cell r="A30">
-            <v>103008</v>
+            <v>103007</v>
           </cell>
           <cell r="B30" t="str">
-            <v>周转箱</v>
+            <v>冰窖</v>
           </cell>
           <cell r="C30">
             <v>0</v>
@@ -1391,10 +1467,10 @@
         </row>
         <row r="31">
           <cell r="A31">
-            <v>103009</v>
+            <v>103008</v>
           </cell>
           <cell r="B31" t="str">
-            <v>冰窖</v>
+            <v>周转箱</v>
           </cell>
           <cell r="C31">
             <v>0</v>
@@ -1402,10 +1478,10 @@
         </row>
         <row r="32">
           <cell r="A32">
-            <v>103012</v>
+            <v>103009</v>
           </cell>
           <cell r="B32" t="str">
-            <v>马车站</v>
+            <v>冰窖</v>
           </cell>
           <cell r="C32">
             <v>0</v>
@@ -1413,10 +1489,10 @@
         </row>
         <row r="33">
           <cell r="A33">
-            <v>103013</v>
+            <v>103012</v>
           </cell>
           <cell r="B33" t="str">
-            <v>喂食器</v>
+            <v>马车站</v>
           </cell>
           <cell r="C33">
             <v>0</v>
@@ -1424,10 +1500,10 @@
         </row>
         <row r="34">
           <cell r="A34">
-            <v>104001</v>
+            <v>103013</v>
           </cell>
           <cell r="B34" t="str">
-            <v>水井</v>
+            <v>喂食器</v>
           </cell>
           <cell r="C34">
             <v>0</v>
@@ -1435,10 +1511,10 @@
         </row>
         <row r="35">
           <cell r="A35">
-            <v>104002</v>
+            <v>104001</v>
           </cell>
           <cell r="B35" t="str">
-            <v>讲台</v>
+            <v>水井</v>
           </cell>
           <cell r="C35">
             <v>0</v>
@@ -1446,10 +1522,10 @@
         </row>
         <row r="36">
           <cell r="A36">
-            <v>104004</v>
+            <v>104002</v>
           </cell>
           <cell r="B36" t="str">
-            <v>布道台</v>
+            <v>讲台</v>
           </cell>
           <cell r="C36">
             <v>0</v>
@@ -1457,10 +1533,10 @@
         </row>
         <row r="37">
           <cell r="A37">
-            <v>104005</v>
+            <v>104004</v>
           </cell>
           <cell r="B37" t="str">
-            <v>墓地</v>
+            <v>布道台</v>
           </cell>
           <cell r="C37">
             <v>0</v>
@@ -1468,10 +1544,10 @@
         </row>
         <row r="38">
           <cell r="A38">
-            <v>104007</v>
+            <v>104005</v>
           </cell>
           <cell r="B38" t="str">
-            <v>诊断台</v>
+            <v>墓地</v>
           </cell>
           <cell r="C38">
             <v>0</v>
@@ -1479,10 +1555,10 @@
         </row>
         <row r="39">
           <cell r="A39">
-            <v>104008</v>
+            <v>104007</v>
           </cell>
           <cell r="B39" t="str">
-            <v>医疗床</v>
+            <v>诊断台</v>
           </cell>
           <cell r="C39">
             <v>0</v>
@@ -1490,10 +1566,10 @@
         </row>
         <row r="40">
           <cell r="A40">
-            <v>104011</v>
+            <v>104008</v>
           </cell>
           <cell r="B40" t="str">
-            <v>篝火堆</v>
+            <v>医疗床</v>
           </cell>
           <cell r="C40">
             <v>0</v>
@@ -1501,10 +1577,10 @@
         </row>
         <row r="41">
           <cell r="A41">
-            <v>104012</v>
+            <v>104011</v>
           </cell>
           <cell r="B41" t="str">
-            <v>火把</v>
+            <v>篝火堆</v>
           </cell>
           <cell r="C41">
             <v>0</v>
@@ -1512,10 +1588,10 @@
         </row>
         <row r="42">
           <cell r="A42">
-            <v>104013</v>
+            <v>104012</v>
           </cell>
           <cell r="B42" t="str">
-            <v>火盆</v>
+            <v>火把</v>
           </cell>
           <cell r="C42">
             <v>0</v>
@@ -1523,10 +1599,10 @@
         </row>
         <row r="43">
           <cell r="A43">
-            <v>104014</v>
+            <v>104013</v>
           </cell>
           <cell r="B43" t="str">
-            <v>壁炉</v>
+            <v>火盆</v>
           </cell>
           <cell r="C43">
             <v>0</v>
@@ -1534,10 +1610,10 @@
         </row>
         <row r="44">
           <cell r="A44">
-            <v>104015</v>
+            <v>104014</v>
           </cell>
           <cell r="B44" t="str">
-            <v>椅子</v>
+            <v>壁炉</v>
           </cell>
           <cell r="C44">
             <v>0</v>
@@ -1545,10 +1621,10 @@
         </row>
         <row r="45">
           <cell r="A45">
-            <v>104016</v>
+            <v>104015</v>
           </cell>
           <cell r="B45" t="str">
-            <v>餐桌</v>
+            <v>椅子</v>
           </cell>
           <cell r="C45">
             <v>0</v>
@@ -1556,10 +1632,10 @@
         </row>
         <row r="46">
           <cell r="A46">
-            <v>104017</v>
+            <v>104016</v>
           </cell>
           <cell r="B46" t="str">
-            <v>研究台</v>
+            <v>餐桌</v>
           </cell>
           <cell r="C46">
             <v>0</v>
@@ -1567,10 +1643,10 @@
         </row>
         <row r="47">
           <cell r="A47">
-            <v>104018</v>
+            <v>104017</v>
           </cell>
           <cell r="B47" t="str">
-            <v>小花盆</v>
+            <v>研究台</v>
           </cell>
           <cell r="C47">
             <v>0</v>
@@ -1578,10 +1654,10 @@
         </row>
         <row r="48">
           <cell r="A48">
-            <v>104019</v>
+            <v>104018</v>
           </cell>
           <cell r="B48" t="str">
-            <v>接待台</v>
+            <v>小花盆</v>
           </cell>
           <cell r="C48">
             <v>0</v>
@@ -1589,10 +1665,10 @@
         </row>
         <row r="49">
           <cell r="A49">
-            <v>104020</v>
+            <v>104019</v>
           </cell>
           <cell r="B49" t="str">
-            <v>宴会桌</v>
+            <v>接待台</v>
           </cell>
           <cell r="C49">
             <v>0</v>
@@ -1600,10 +1676,10 @@
         </row>
         <row r="50">
           <cell r="A50">
-            <v>104021</v>
+            <v>104020</v>
           </cell>
           <cell r="B50" t="str">
-            <v>厕所</v>
+            <v>宴会桌</v>
           </cell>
           <cell r="C50">
             <v>0</v>
@@ -1611,10 +1687,10 @@
         </row>
         <row r="51">
           <cell r="A51">
-            <v>104022</v>
+            <v>104021</v>
           </cell>
           <cell r="B51" t="str">
-            <v>英雄纪念碑</v>
+            <v>厕所</v>
           </cell>
           <cell r="C51">
             <v>0</v>
@@ -1622,10 +1698,10 @@
         </row>
         <row r="52">
           <cell r="A52">
-            <v>104023</v>
+            <v>104022</v>
           </cell>
           <cell r="B52" t="str">
-            <v>扑克桌</v>
+            <v>英雄纪念碑</v>
           </cell>
           <cell r="C52">
             <v>0</v>
@@ -1633,10 +1709,10 @@
         </row>
         <row r="53">
           <cell r="A53">
-            <v>104024</v>
+            <v>104023</v>
           </cell>
           <cell r="B53" t="str">
-            <v>高级扑克桌</v>
+            <v>扑克桌</v>
           </cell>
           <cell r="C53">
             <v>0</v>
@@ -1644,10 +1720,10 @@
         </row>
         <row r="54">
           <cell r="A54">
-            <v>104025</v>
+            <v>104024</v>
           </cell>
           <cell r="B54" t="str">
-            <v>豪华扑克桌</v>
+            <v>高级扑克桌</v>
           </cell>
           <cell r="C54">
             <v>0</v>
@@ -1655,10 +1731,10 @@
         </row>
         <row r="55">
           <cell r="A55">
-            <v>104026</v>
+            <v>104025</v>
           </cell>
           <cell r="B55" t="str">
-            <v>幸运轮盘</v>
+            <v>豪华扑克桌</v>
           </cell>
           <cell r="C55">
             <v>0</v>
@@ -1666,10 +1742,10 @@
         </row>
         <row r="56">
           <cell r="A56">
-            <v>104027</v>
+            <v>104026</v>
           </cell>
           <cell r="B56" t="str">
-            <v>公共浴场</v>
+            <v>幸运轮盘</v>
           </cell>
           <cell r="C56">
             <v>0</v>
@@ -1677,10 +1753,10 @@
         </row>
         <row r="57">
           <cell r="A57">
-            <v>104028</v>
+            <v>104027</v>
           </cell>
           <cell r="B57" t="str">
-            <v>花盆</v>
+            <v>公共浴场</v>
           </cell>
           <cell r="C57">
             <v>0</v>
@@ -1688,10 +1764,10 @@
         </row>
         <row r="58">
           <cell r="A58">
-            <v>104029</v>
+            <v>104028</v>
           </cell>
           <cell r="B58" t="str">
-            <v>灌木花盆</v>
+            <v>花盆</v>
           </cell>
           <cell r="C58">
             <v>0</v>
@@ -1699,10 +1775,10 @@
         </row>
         <row r="59">
           <cell r="A59">
-            <v>104030</v>
+            <v>104029</v>
           </cell>
           <cell r="B59" t="str">
-            <v>种树花盆</v>
+            <v>灌木花盆</v>
           </cell>
           <cell r="C59">
             <v>0</v>
@@ -1710,10 +1786,10 @@
         </row>
         <row r="60">
           <cell r="A60">
-            <v>105001</v>
+            <v>104030</v>
           </cell>
           <cell r="B60" t="str">
-            <v>农田</v>
+            <v>种树花盆</v>
           </cell>
           <cell r="C60">
             <v>0</v>
@@ -1721,10 +1797,10 @@
         </row>
         <row r="61">
           <cell r="A61">
-            <v>105002</v>
+            <v>104031</v>
           </cell>
           <cell r="B61" t="str">
-            <v>果园</v>
+            <v>木牌</v>
           </cell>
           <cell r="C61">
             <v>0</v>
@@ -1732,10 +1808,10 @@
         </row>
         <row r="62">
           <cell r="A62">
-            <v>105003</v>
+            <v>105001</v>
           </cell>
           <cell r="B62" t="str">
-            <v>牧场</v>
+            <v>农田</v>
           </cell>
           <cell r="C62">
             <v>0</v>
@@ -1743,10 +1819,10 @@
         </row>
         <row r="63">
           <cell r="A63">
-            <v>105004</v>
+            <v>105002</v>
           </cell>
           <cell r="B63" t="str">
-            <v>渔人码头</v>
+            <v>果园</v>
           </cell>
           <cell r="C63">
             <v>0</v>
@@ -1754,10 +1830,10 @@
         </row>
         <row r="64">
           <cell r="A64">
-            <v>105005</v>
+            <v>105003</v>
           </cell>
           <cell r="B64" t="str">
-            <v>猎人营地</v>
+            <v>牧场</v>
           </cell>
           <cell r="C64">
             <v>0</v>
@@ -1765,10 +1841,10 @@
         </row>
         <row r="65">
           <cell r="A65">
-            <v>105006</v>
+            <v>105004</v>
           </cell>
           <cell r="B65" t="str">
-            <v>采集营地</v>
+            <v>渔人码头</v>
           </cell>
           <cell r="C65">
             <v>0</v>
@@ -1776,10 +1852,10 @@
         </row>
         <row r="66">
           <cell r="A66">
-            <v>105007</v>
+            <v>105005</v>
           </cell>
           <cell r="B66" t="str">
-            <v>劈材桩</v>
+            <v>猎人营地</v>
           </cell>
           <cell r="C66">
             <v>0</v>
@@ -1787,10 +1863,10 @@
         </row>
         <row r="67">
           <cell r="A67">
-            <v>105008</v>
+            <v>105006</v>
           </cell>
           <cell r="B67" t="str">
-            <v>护林营地</v>
+            <v>采集营地</v>
           </cell>
           <cell r="C67">
             <v>0</v>
@@ -1798,10 +1874,10 @@
         </row>
         <row r="68">
           <cell r="A68">
-            <v>105009</v>
+            <v>105007</v>
           </cell>
           <cell r="B68" t="str">
-            <v>采药营地</v>
+            <v>劈材桩</v>
           </cell>
           <cell r="C68">
             <v>0</v>
@@ -1809,10 +1885,10 @@
         </row>
         <row r="69">
           <cell r="A69">
-            <v>105010</v>
+            <v>105008</v>
           </cell>
           <cell r="B69" t="str">
-            <v>制造台</v>
+            <v>护林营地</v>
           </cell>
           <cell r="C69">
             <v>0</v>
@@ -1820,10 +1896,10 @@
         </row>
         <row r="70">
           <cell r="A70">
-            <v>105011</v>
+            <v>105009</v>
           </cell>
           <cell r="B70" t="str">
-            <v>缝纫台</v>
+            <v>采药营地</v>
           </cell>
           <cell r="C70">
             <v>0</v>
@@ -1831,10 +1907,10 @@
         </row>
         <row r="71">
           <cell r="A71">
-            <v>105012</v>
+            <v>105010</v>
           </cell>
           <cell r="B71" t="str">
-            <v>酿酒桶</v>
+            <v>制造台</v>
           </cell>
           <cell r="C71">
             <v>0</v>
@@ -1842,10 +1918,10 @@
         </row>
         <row r="72">
           <cell r="A72">
-            <v>105013</v>
+            <v>105011</v>
           </cell>
           <cell r="B72" t="str">
-            <v>矿井</v>
+            <v>缝纫台</v>
           </cell>
           <cell r="C72">
             <v>0</v>
@@ -1853,10 +1929,10 @@
         </row>
         <row r="73">
           <cell r="A73">
-            <v>105014</v>
+            <v>105012</v>
           </cell>
           <cell r="B73" t="str">
-            <v>采石场</v>
+            <v>酿酒桶</v>
           </cell>
           <cell r="C73">
             <v>0</v>
@@ -1864,10 +1940,10 @@
         </row>
         <row r="74">
           <cell r="A74">
-            <v>105015</v>
+            <v>105013</v>
           </cell>
           <cell r="B74" t="str">
-            <v>堆肥桶</v>
+            <v>矿井</v>
           </cell>
           <cell r="C74">
             <v>0</v>
@@ -1875,10 +1951,10 @@
         </row>
         <row r="75">
           <cell r="A75">
-            <v>105016</v>
+            <v>105014</v>
           </cell>
           <cell r="B75" t="str">
-            <v>烹饪台</v>
+            <v>采石场</v>
           </cell>
           <cell r="C75">
             <v>0</v>
@@ -1886,10 +1962,10 @@
         </row>
         <row r="76">
           <cell r="A76">
-            <v>105017</v>
+            <v>105015</v>
           </cell>
           <cell r="B76" t="str">
-            <v>捕兽夹</v>
+            <v>堆肥桶</v>
           </cell>
           <cell r="C76">
             <v>0</v>
@@ -1897,10 +1973,10 @@
         </row>
         <row r="77">
           <cell r="A77">
-            <v>105018</v>
+            <v>105016</v>
           </cell>
           <cell r="B77" t="str">
-            <v>蟹笼</v>
+            <v>烹饪台</v>
           </cell>
           <cell r="C77">
             <v>0</v>
@@ -1908,10 +1984,10 @@
         </row>
         <row r="78">
           <cell r="A78">
-            <v>105019</v>
+            <v>105017</v>
           </cell>
           <cell r="B78" t="str">
-            <v>取水点</v>
+            <v>捕兽夹</v>
           </cell>
           <cell r="C78">
             <v>0</v>
@@ -1919,10 +1995,10 @@
         </row>
         <row r="79">
           <cell r="A79">
-            <v>105020</v>
+            <v>105018</v>
           </cell>
           <cell r="B79" t="str">
-            <v>采石点</v>
+            <v>蟹笼</v>
           </cell>
           <cell r="C79">
             <v>0</v>
@@ -1930,10 +2006,10 @@
         </row>
         <row r="80">
           <cell r="A80">
-            <v>105021</v>
+            <v>105019</v>
           </cell>
           <cell r="B80" t="str">
-            <v>挖掘点</v>
+            <v>取水点</v>
           </cell>
           <cell r="C80">
             <v>0</v>
@@ -1941,10 +2017,10 @@
         </row>
         <row r="81">
           <cell r="A81">
-            <v>105022</v>
+            <v>105020</v>
           </cell>
           <cell r="B81" t="str">
-            <v>造陆点</v>
+            <v>采石点</v>
           </cell>
           <cell r="C81">
             <v>0</v>
@@ -1952,10 +2028,10 @@
         </row>
         <row r="82">
           <cell r="A82">
-            <v>105023</v>
+            <v>105021</v>
           </cell>
           <cell r="B82" t="str">
-            <v>蜂房</v>
+            <v>挖掘点</v>
           </cell>
           <cell r="C82">
             <v>0</v>
@@ -1963,10 +2039,10 @@
         </row>
         <row r="83">
           <cell r="A83">
-            <v>105024</v>
+            <v>105022</v>
           </cell>
           <cell r="B83" t="str">
-            <v>雕像座</v>
+            <v>造陆点</v>
           </cell>
           <cell r="C83">
             <v>0</v>
@@ -1974,10 +2050,10 @@
         </row>
         <row r="84">
           <cell r="A84">
-            <v>105025</v>
+            <v>105023</v>
           </cell>
           <cell r="B84" t="str">
-            <v>炼药锅</v>
+            <v>蜂房</v>
           </cell>
           <cell r="C84">
             <v>0</v>
@@ -1985,10 +2061,10 @@
         </row>
         <row r="85">
           <cell r="A85">
-            <v>105026</v>
+            <v>105024</v>
           </cell>
           <cell r="B85" t="str">
-            <v>码头</v>
+            <v>雕像座</v>
           </cell>
           <cell r="C85">
             <v>0</v>
@@ -1996,10 +2072,10 @@
         </row>
         <row r="86">
           <cell r="A86">
-            <v>105027</v>
+            <v>105025</v>
           </cell>
           <cell r="B86" t="str">
-            <v>出海口</v>
+            <v>炼药锅</v>
           </cell>
           <cell r="C86">
             <v>0</v>
@@ -2007,10 +2083,10 @@
         </row>
         <row r="87">
           <cell r="A87">
-            <v>105028</v>
+            <v>105026</v>
           </cell>
           <cell r="B87" t="str">
-            <v>熔炉</v>
+            <v>码头</v>
           </cell>
           <cell r="C87">
             <v>0</v>
@@ -2018,10 +2094,10 @@
         </row>
         <row r="88">
           <cell r="A88">
-            <v>105029</v>
+            <v>105027</v>
           </cell>
           <cell r="B88" t="str">
-            <v>磨坊</v>
+            <v>出海口</v>
           </cell>
           <cell r="C88">
             <v>0</v>
@@ -2029,10 +2105,10 @@
         </row>
         <row r="89">
           <cell r="A89">
-            <v>105030</v>
+            <v>105028</v>
           </cell>
           <cell r="B89" t="str">
-            <v>蘑菇箱</v>
+            <v>熔炉</v>
           </cell>
           <cell r="C89">
             <v>0</v>
@@ -2040,10 +2116,10 @@
         </row>
         <row r="90">
           <cell r="A90">
-            <v>105031</v>
+            <v>105029</v>
           </cell>
           <cell r="B90" t="str">
-            <v>资源搜集点</v>
+            <v>磨坊</v>
           </cell>
           <cell r="C90">
             <v>0</v>
@@ -2051,10 +2127,10 @@
         </row>
         <row r="91">
           <cell r="A91">
-            <v>105032</v>
+            <v>105030</v>
           </cell>
           <cell r="B91" t="str">
-            <v>磨坊</v>
+            <v>蘑菇箱</v>
           </cell>
           <cell r="C91">
             <v>0</v>
@@ -2062,10 +2138,10 @@
         </row>
         <row r="92">
           <cell r="A92">
-            <v>106001</v>
+            <v>105031</v>
           </cell>
           <cell r="B92" t="str">
-            <v>军营</v>
+            <v>资源搜集点</v>
           </cell>
           <cell r="C92">
             <v>0</v>
@@ -2073,10 +2149,10 @@
         </row>
         <row r="93">
           <cell r="A93">
-            <v>106002</v>
+            <v>105032</v>
           </cell>
           <cell r="B93" t="str">
-            <v>牢房</v>
+            <v>磨坊</v>
           </cell>
           <cell r="C93">
             <v>0</v>
@@ -2084,10 +2160,10 @@
         </row>
         <row r="94">
           <cell r="A94">
-            <v>106003</v>
+            <v>106001</v>
           </cell>
           <cell r="B94" t="str">
-            <v>大炮</v>
+            <v>军营</v>
           </cell>
           <cell r="C94">
             <v>0</v>
@@ -2095,10 +2171,10 @@
         </row>
         <row r="95">
           <cell r="A95">
-            <v>106004</v>
+            <v>106002</v>
           </cell>
           <cell r="B95" t="str">
-            <v>野营</v>
+            <v>牢房</v>
           </cell>
           <cell r="C95">
             <v>0</v>
@@ -2106,10 +2182,10 @@
         </row>
         <row r="96">
           <cell r="A96">
-            <v>106005</v>
+            <v>106003</v>
           </cell>
           <cell r="B96" t="str">
-            <v>王座</v>
+            <v>大炮</v>
           </cell>
           <cell r="C96">
             <v>0</v>
@@ -2117,10 +2193,10 @@
         </row>
         <row r="97">
           <cell r="A97">
-            <v>106006</v>
+            <v>106004</v>
           </cell>
           <cell r="B97" t="str">
-            <v>地雷</v>
+            <v>野营</v>
           </cell>
           <cell r="C97">
             <v>0</v>
@@ -2128,10 +2204,10 @@
         </row>
         <row r="98">
           <cell r="A98">
-            <v>106007</v>
+            <v>106005</v>
           </cell>
           <cell r="B98" t="str">
-            <v>水晶球</v>
+            <v>王座</v>
           </cell>
           <cell r="C98">
             <v>0</v>
@@ -2139,10 +2215,10 @@
         </row>
         <row r="99">
           <cell r="A99">
-            <v>106008</v>
+            <v>106006</v>
           </cell>
           <cell r="B99" t="str">
-            <v>训练场</v>
+            <v>地雷</v>
           </cell>
           <cell r="C99">
             <v>0</v>
@@ -2150,10 +2226,10 @@
         </row>
         <row r="100">
           <cell r="A100">
-            <v>107001</v>
+            <v>106007</v>
           </cell>
           <cell r="B100" t="str">
-            <v>废弃矿井</v>
+            <v>水晶球</v>
           </cell>
           <cell r="C100">
             <v>0</v>
@@ -2161,10 +2237,10 @@
         </row>
         <row r="101">
           <cell r="A101">
-            <v>107003</v>
+            <v>106008</v>
           </cell>
           <cell r="B101" t="str">
-            <v>墓碑</v>
+            <v>训练场</v>
           </cell>
           <cell r="C101">
             <v>0</v>
@@ -2172,10 +2248,10 @@
         </row>
         <row r="102">
           <cell r="A102">
-            <v>107004</v>
+            <v>107001</v>
           </cell>
           <cell r="B102" t="str">
-            <v>强盗营地</v>
+            <v>废弃矿井</v>
           </cell>
           <cell r="C102">
             <v>0</v>
@@ -2183,10 +2259,10 @@
         </row>
         <row r="103">
           <cell r="A103">
-            <v>107005</v>
+            <v>107003</v>
           </cell>
           <cell r="B103" t="str">
-            <v>军营</v>
+            <v>墓碑</v>
           </cell>
           <cell r="C103">
             <v>0</v>
@@ -2194,10 +2270,10 @@
         </row>
         <row r="104">
           <cell r="A104">
-            <v>108001</v>
+            <v>107004</v>
           </cell>
           <cell r="B104" t="str">
-            <v>古墓</v>
+            <v>强盗营地</v>
           </cell>
           <cell r="C104">
             <v>0</v>
@@ -2205,10 +2281,10 @@
         </row>
         <row r="105">
           <cell r="A105">
-            <v>108002</v>
+            <v>107005</v>
           </cell>
           <cell r="B105" t="str">
-            <v>巨型蜂巢</v>
+            <v>军营</v>
           </cell>
           <cell r="C105">
             <v>0</v>
@@ -2216,10 +2292,10 @@
         </row>
         <row r="106">
           <cell r="A106">
-            <v>108003</v>
+            <v>108001</v>
           </cell>
           <cell r="B106" t="str">
-            <v>金字塔</v>
+            <v>古墓</v>
           </cell>
           <cell r="C106">
             <v>0</v>
@@ -2227,10 +2303,10 @@
         </row>
         <row r="107">
           <cell r="A107">
-            <v>108004</v>
+            <v>108002</v>
           </cell>
           <cell r="B107" t="str">
-            <v>巨型蘑菇</v>
+            <v>巨型蜂巢</v>
           </cell>
           <cell r="C107">
             <v>0</v>
@@ -2238,10 +2314,10 @@
         </row>
         <row r="108">
           <cell r="A108">
-            <v>108005</v>
+            <v>108003</v>
           </cell>
           <cell r="B108" t="str">
-            <v>巨树</v>
+            <v>金字塔</v>
           </cell>
           <cell r="C108">
             <v>0</v>
@@ -2249,10 +2325,10 @@
         </row>
         <row r="109">
           <cell r="A109">
-            <v>108006</v>
+            <v>108004</v>
           </cell>
           <cell r="B109" t="str">
-            <v>巨型蛋</v>
+            <v>巨型蘑菇</v>
           </cell>
           <cell r="C109">
             <v>0</v>
@@ -2260,10 +2336,10 @@
         </row>
         <row r="110">
           <cell r="A110">
-            <v>108007</v>
+            <v>108005</v>
           </cell>
           <cell r="B110" t="str">
-            <v>沉船遗迹</v>
+            <v>巨树</v>
           </cell>
           <cell r="C110">
             <v>0</v>
@@ -2271,10 +2347,10 @@
         </row>
         <row r="111">
           <cell r="A111">
-            <v>108008</v>
+            <v>108006</v>
           </cell>
           <cell r="B111" t="str">
-            <v>蚁穴</v>
+            <v>巨型蛋</v>
           </cell>
           <cell r="C111">
             <v>0</v>
@@ -2282,10 +2358,10 @@
         </row>
         <row r="112">
           <cell r="A112">
-            <v>108009</v>
+            <v>108007</v>
           </cell>
           <cell r="B112" t="str">
-            <v>图腾之柱</v>
+            <v>沉船遗迹</v>
           </cell>
           <cell r="C112">
             <v>0</v>
@@ -2293,10 +2369,10 @@
         </row>
         <row r="113">
           <cell r="A113">
-            <v>108010</v>
+            <v>108008</v>
           </cell>
           <cell r="B113" t="str">
-            <v>布道台</v>
+            <v>蚁穴</v>
           </cell>
           <cell r="C113">
             <v>0</v>
@@ -2304,10 +2380,10 @@
         </row>
         <row r="114">
           <cell r="A114">
-            <v>108011</v>
+            <v>108009</v>
           </cell>
           <cell r="B114" t="str">
-            <v>红蚁穴</v>
+            <v>图腾之柱</v>
           </cell>
           <cell r="C114">
             <v>0</v>
@@ -2315,10 +2391,10 @@
         </row>
         <row r="115">
           <cell r="A115">
-            <v>108012</v>
+            <v>108010</v>
           </cell>
           <cell r="B115" t="str">
-            <v>国王的永恒圣殿</v>
+            <v>布道台</v>
           </cell>
           <cell r="C115">
             <v>0</v>
@@ -2326,10 +2402,10 @@
         </row>
         <row r="116">
           <cell r="A116">
-            <v>109005</v>
+            <v>108011</v>
           </cell>
           <cell r="B116" t="str">
-            <v>国库</v>
+            <v>红蚁穴</v>
           </cell>
           <cell r="C116">
             <v>0</v>
@@ -2337,10 +2413,10 @@
         </row>
         <row r="117">
           <cell r="A117">
-            <v>110001</v>
+            <v>108012</v>
           </cell>
           <cell r="B117" t="str">
-            <v>小城堡</v>
+            <v>国王的永恒圣殿</v>
           </cell>
           <cell r="C117">
             <v>0</v>
@@ -2348,10 +2424,10 @@
         </row>
         <row r="118">
           <cell r="A118">
-            <v>110002</v>
+            <v>109005</v>
           </cell>
           <cell r="B118" t="str">
-            <v>大城堡</v>
+            <v>国库</v>
           </cell>
           <cell r="C118">
             <v>0</v>
@@ -2359,10 +2435,10 @@
         </row>
         <row r="119">
           <cell r="A119">
-            <v>110003</v>
+            <v>110001</v>
           </cell>
           <cell r="B119" t="str">
-            <v>小村庄</v>
+            <v>小城堡</v>
           </cell>
           <cell r="C119">
             <v>0</v>
@@ -2370,10 +2446,10 @@
         </row>
         <row r="120">
           <cell r="A120">
-            <v>110004</v>
+            <v>110002</v>
           </cell>
           <cell r="B120" t="str">
-            <v>大村庄</v>
+            <v>大城堡</v>
           </cell>
           <cell r="C120">
             <v>0</v>
@@ -2381,10 +2457,10 @@
         </row>
         <row r="121">
           <cell r="A121">
-            <v>110005</v>
+            <v>110003</v>
           </cell>
           <cell r="B121" t="str">
-            <v>渔村</v>
+            <v>小村庄</v>
           </cell>
           <cell r="C121">
             <v>0</v>
@@ -2392,10 +2468,10 @@
         </row>
         <row r="122">
           <cell r="A122">
-            <v>110006</v>
+            <v>110004</v>
           </cell>
           <cell r="B122" t="str">
-            <v>小部落</v>
+            <v>大村庄</v>
           </cell>
           <cell r="C122">
             <v>0</v>
@@ -2403,10 +2479,10 @@
         </row>
         <row r="123">
           <cell r="A123">
-            <v>110007</v>
+            <v>110005</v>
           </cell>
           <cell r="B123" t="str">
-            <v>大部落</v>
+            <v>渔村</v>
           </cell>
           <cell r="C123">
             <v>0</v>
@@ -2414,10 +2490,10 @@
         </row>
         <row r="124">
           <cell r="A124">
-            <v>110008</v>
+            <v>110006</v>
           </cell>
           <cell r="B124" t="str">
-            <v>龙之试炼柱</v>
+            <v>小部落</v>
           </cell>
           <cell r="C124">
             <v>0</v>
@@ -2425,10 +2501,10 @@
         </row>
         <row r="125">
           <cell r="A125">
-            <v>110009</v>
+            <v>110007</v>
           </cell>
           <cell r="B125" t="str">
-            <v>要塞</v>
+            <v>大部落</v>
           </cell>
           <cell r="C125">
             <v>0</v>
@@ -2436,10 +2512,10 @@
         </row>
         <row r="126">
           <cell r="A126">
-            <v>110010</v>
+            <v>110008</v>
           </cell>
           <cell r="B126" t="str">
-            <v>战场据点</v>
+            <v>龙之试炼柱</v>
           </cell>
           <cell r="C126">
             <v>0</v>
@@ -2447,10 +2523,10 @@
         </row>
         <row r="127">
           <cell r="A127">
-            <v>110011</v>
+            <v>110009</v>
           </cell>
           <cell r="B127" t="str">
-            <v>远征营地</v>
+            <v>要塞</v>
           </cell>
           <cell r="C127">
             <v>0</v>
@@ -2458,10 +2534,10 @@
         </row>
         <row r="128">
           <cell r="A128">
-            <v>110012</v>
+            <v>110010</v>
           </cell>
           <cell r="B128" t="str">
-            <v>被敌人占领的战场据点</v>
+            <v>战场据点</v>
           </cell>
           <cell r="C128">
             <v>0</v>
@@ -2469,10 +2545,10 @@
         </row>
         <row r="129">
           <cell r="A129">
-            <v>111001</v>
+            <v>110011</v>
           </cell>
           <cell r="B129" t="str">
-            <v>方尖碑</v>
+            <v>远征营地</v>
           </cell>
           <cell r="C129">
             <v>0</v>
@@ -2480,10 +2556,10 @@
         </row>
         <row r="130">
           <cell r="A130">
-            <v>111002</v>
+            <v>110012</v>
           </cell>
           <cell r="B130" t="str">
-            <v>泰坦祭坛</v>
+            <v>被敌人占领的战场据点</v>
           </cell>
           <cell r="C130">
             <v>0</v>
@@ -2491,10 +2567,10 @@
         </row>
         <row r="131">
           <cell r="A131">
-            <v>111003</v>
+            <v>111001</v>
           </cell>
           <cell r="B131" t="str">
-            <v>光明祭坛</v>
+            <v>方尖碑</v>
           </cell>
           <cell r="C131">
             <v>0</v>
@@ -2502,10 +2578,10 @@
         </row>
         <row r="132">
           <cell r="A132">
-            <v>111004</v>
+            <v>111002</v>
           </cell>
           <cell r="B132" t="str">
-            <v>黑暗祭坛</v>
+            <v>泰坦祭坛</v>
           </cell>
           <cell r="C132">
             <v>0</v>
@@ -2513,10 +2589,10 @@
         </row>
         <row r="133">
           <cell r="A133">
-            <v>111005</v>
+            <v>111003</v>
           </cell>
           <cell r="B133" t="str">
-            <v>永恒圣殿</v>
+            <v>光明祭坛</v>
           </cell>
           <cell r="C133">
             <v>0</v>
@@ -2524,10 +2600,10 @@
         </row>
         <row r="134">
           <cell r="A134">
-            <v>112001</v>
+            <v>111004</v>
           </cell>
           <cell r="B134" t="str">
-            <v>旗帜</v>
+            <v>黑暗祭坛</v>
           </cell>
           <cell r="C134">
             <v>0</v>
@@ -2535,10 +2611,10 @@
         </row>
         <row r="135">
           <cell r="A135">
-            <v>113001</v>
+            <v>111005</v>
           </cell>
           <cell r="B135" t="str">
-            <v>地板</v>
+            <v>永恒圣殿</v>
           </cell>
           <cell r="C135">
             <v>0</v>
@@ -2546,10 +2622,10 @@
         </row>
         <row r="136">
           <cell r="A136">
-            <v>113002</v>
+            <v>112001</v>
           </cell>
           <cell r="B136" t="str">
-            <v>石质地板</v>
+            <v>旗帜</v>
           </cell>
           <cell r="C136">
             <v>0</v>
@@ -2557,10 +2633,10 @@
         </row>
         <row r="137">
           <cell r="A137">
-            <v>113003</v>
+            <v>113001</v>
           </cell>
           <cell r="B137" t="str">
-            <v>铁质地板</v>
+            <v>地板</v>
           </cell>
           <cell r="C137">
             <v>0</v>
@@ -2568,10 +2644,10 @@
         </row>
         <row r="138">
           <cell r="A138">
-            <v>113004</v>
+            <v>113002</v>
           </cell>
           <cell r="B138" t="str">
-            <v>银质地板</v>
+            <v>石质地板</v>
           </cell>
           <cell r="C138">
             <v>0</v>
@@ -2579,10 +2655,10 @@
         </row>
         <row r="139">
           <cell r="A139">
-            <v>113005</v>
+            <v>113003</v>
           </cell>
           <cell r="B139" t="str">
-            <v>金质地板</v>
+            <v>铁质地板</v>
           </cell>
           <cell r="C139">
             <v>0</v>
@@ -2590,32 +2666,32 @@
         </row>
         <row r="140">
           <cell r="A140">
-            <v>301001</v>
+            <v>113004</v>
           </cell>
           <cell r="B140" t="str">
-            <v>菜豆</v>
+            <v>银质地板</v>
           </cell>
           <cell r="C140">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>301002</v>
+            <v>113005</v>
           </cell>
           <cell r="B141" t="str">
-            <v>卷心菜</v>
+            <v>金质地板</v>
           </cell>
           <cell r="C141">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>301003</v>
+            <v>301001</v>
           </cell>
           <cell r="B142" t="str">
-            <v>辣椒</v>
+            <v>菜豆</v>
           </cell>
           <cell r="C142">
             <v>1</v>
@@ -2623,10 +2699,10 @@
         </row>
         <row r="143">
           <cell r="A143">
-            <v>301004</v>
+            <v>301002</v>
           </cell>
           <cell r="B143" t="str">
-            <v>南瓜</v>
+            <v>卷心菜</v>
           </cell>
           <cell r="C143">
             <v>1</v>
@@ -2634,10 +2710,10 @@
         </row>
         <row r="144">
           <cell r="A144">
-            <v>301005</v>
+            <v>301003</v>
           </cell>
           <cell r="B144" t="str">
-            <v>笋瓜</v>
+            <v>辣椒</v>
           </cell>
           <cell r="C144">
             <v>1</v>
@@ -2645,10 +2721,10 @@
         </row>
         <row r="145">
           <cell r="A145">
-            <v>301006</v>
+            <v>301004</v>
           </cell>
           <cell r="B145" t="str">
-            <v>蘑菇</v>
+            <v>南瓜</v>
           </cell>
           <cell r="C145">
             <v>1</v>
@@ -2656,10 +2732,10 @@
         </row>
         <row r="146">
           <cell r="A146">
-            <v>301007</v>
+            <v>301005</v>
           </cell>
           <cell r="B146" t="str">
-            <v>洋葱</v>
+            <v>笋瓜</v>
           </cell>
           <cell r="C146">
             <v>1</v>
@@ -2667,10 +2743,10 @@
         </row>
         <row r="147">
           <cell r="A147">
-            <v>302001</v>
+            <v>301006</v>
           </cell>
           <cell r="B147" t="str">
-            <v>玉米</v>
+            <v>蘑菇</v>
           </cell>
           <cell r="C147">
             <v>1</v>
@@ -2678,10 +2754,10 @@
         </row>
         <row r="148">
           <cell r="A148">
-            <v>302002</v>
+            <v>301007</v>
           </cell>
           <cell r="B148" t="str">
-            <v>土豆</v>
+            <v>洋葱</v>
           </cell>
           <cell r="C148">
             <v>1</v>
@@ -2689,10 +2765,10 @@
         </row>
         <row r="149">
           <cell r="A149">
-            <v>302003</v>
+            <v>302001</v>
           </cell>
           <cell r="B149" t="str">
-            <v>小麦</v>
+            <v>玉米</v>
           </cell>
           <cell r="C149">
             <v>1</v>
@@ -2700,10 +2776,10 @@
         </row>
         <row r="150">
           <cell r="A150">
-            <v>302004</v>
+            <v>302002</v>
           </cell>
           <cell r="B150" t="str">
-            <v>木薯</v>
+            <v>土豆</v>
           </cell>
           <cell r="C150">
             <v>1</v>
@@ -2711,10 +2787,10 @@
         </row>
         <row r="151">
           <cell r="A151">
-            <v>303001</v>
+            <v>302003</v>
           </cell>
           <cell r="B151" t="str">
-            <v>苹果</v>
+            <v>小麦</v>
           </cell>
           <cell r="C151">
             <v>1</v>
@@ -2722,10 +2798,10 @@
         </row>
         <row r="152">
           <cell r="A152">
-            <v>303002</v>
+            <v>302004</v>
           </cell>
           <cell r="B152" t="str">
-            <v>樱桃</v>
+            <v>木薯</v>
           </cell>
           <cell r="C152">
             <v>1</v>
@@ -2733,10 +2809,10 @@
         </row>
         <row r="153">
           <cell r="A153">
-            <v>303004</v>
+            <v>303001</v>
           </cell>
           <cell r="B153" t="str">
-            <v>梨</v>
+            <v>苹果</v>
           </cell>
           <cell r="C153">
             <v>1</v>
@@ -2744,10 +2820,10 @@
         </row>
         <row r="154">
           <cell r="A154">
-            <v>303006</v>
+            <v>303002</v>
           </cell>
           <cell r="B154" t="str">
-            <v>梅子</v>
+            <v>樱桃</v>
           </cell>
           <cell r="C154">
             <v>1</v>
@@ -2755,10 +2831,10 @@
         </row>
         <row r="155">
           <cell r="A155">
-            <v>303007</v>
+            <v>303004</v>
           </cell>
           <cell r="B155" t="str">
-            <v>核桃</v>
+            <v>梨</v>
           </cell>
           <cell r="C155">
             <v>1</v>
@@ -2766,10 +2842,10 @@
         </row>
         <row r="156">
           <cell r="A156">
-            <v>303009</v>
+            <v>303006</v>
           </cell>
           <cell r="B156" t="str">
-            <v>浆果</v>
+            <v>梅子</v>
           </cell>
           <cell r="C156">
             <v>1</v>
@@ -2777,32 +2853,32 @@
         </row>
         <row r="157">
           <cell r="A157">
-            <v>304001</v>
+            <v>303007</v>
           </cell>
           <cell r="B157" t="str">
-            <v>鱼</v>
+            <v>核桃</v>
           </cell>
           <cell r="C157">
-            <v>2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>304002</v>
+            <v>303009</v>
           </cell>
           <cell r="B158" t="str">
-            <v>肉</v>
+            <v>浆果</v>
           </cell>
           <cell r="C158">
-            <v>2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>304005</v>
+            <v>304001</v>
           </cell>
           <cell r="B159" t="str">
-            <v>鸡蛋</v>
+            <v>鱼</v>
           </cell>
           <cell r="C159">
             <v>2</v>
@@ -2810,10 +2886,10 @@
         </row>
         <row r="160">
           <cell r="A160">
-            <v>304007</v>
+            <v>304002</v>
           </cell>
           <cell r="B160" t="str">
-            <v>螃蟹</v>
+            <v>肉</v>
           </cell>
           <cell r="C160">
             <v>2</v>
@@ -2821,10 +2897,10 @@
         </row>
         <row r="161">
           <cell r="A161">
-            <v>304008</v>
+            <v>304005</v>
           </cell>
           <cell r="B161" t="str">
-            <v>龙虾</v>
+            <v>鸡蛋</v>
           </cell>
           <cell r="C161">
             <v>2</v>
@@ -2832,10 +2908,10 @@
         </row>
         <row r="162">
           <cell r="A162">
-            <v>304009</v>
+            <v>304007</v>
           </cell>
           <cell r="B162" t="str">
-            <v>熏鱼</v>
+            <v>螃蟹</v>
           </cell>
           <cell r="C162">
             <v>2</v>
@@ -2843,10 +2919,10 @@
         </row>
         <row r="163">
           <cell r="A163">
-            <v>304010</v>
+            <v>304008</v>
           </cell>
           <cell r="B163" t="str">
-            <v>熏肉</v>
+            <v>龙虾</v>
           </cell>
           <cell r="C163">
             <v>2</v>
@@ -2854,10 +2930,10 @@
         </row>
         <row r="164">
           <cell r="A164">
-            <v>305001</v>
+            <v>304009</v>
           </cell>
           <cell r="B164" t="str">
-            <v>简单食物</v>
+            <v>熏鱼</v>
           </cell>
           <cell r="C164">
             <v>2</v>
@@ -2865,21 +2941,21 @@
         </row>
         <row r="165">
           <cell r="A165">
-            <v>305002</v>
+            <v>304010</v>
           </cell>
           <cell r="B165" t="str">
-            <v>精致食物</v>
+            <v>熏肉</v>
           </cell>
           <cell r="C165">
-            <v>4</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>305003</v>
+            <v>305001</v>
           </cell>
           <cell r="B166" t="str">
-            <v>黑暗料理</v>
+            <v>简单食物</v>
           </cell>
           <cell r="C166">
             <v>2</v>
@@ -2887,197 +2963,197 @@
         </row>
         <row r="167">
           <cell r="A167">
-            <v>305004</v>
+            <v>305002</v>
           </cell>
           <cell r="B167" t="str">
-            <v>粗糙食物</v>
+            <v>精致食物</v>
           </cell>
           <cell r="C167">
-            <v>1</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>305005</v>
+            <v>305003</v>
           </cell>
           <cell r="B168" t="str">
-            <v>饼干</v>
+            <v>黑暗料理</v>
           </cell>
           <cell r="C168">
-            <v>5</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>305006</v>
+            <v>305004</v>
           </cell>
           <cell r="B169" t="str">
-            <v>蛋糕</v>
+            <v>粗糙食物</v>
           </cell>
           <cell r="C169">
-            <v>10</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>306001</v>
+            <v>305005</v>
           </cell>
           <cell r="B170" t="str">
-            <v>蜂蜜</v>
+            <v>饼干</v>
           </cell>
           <cell r="C170">
-            <v>3</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>401001</v>
+            <v>305006</v>
           </cell>
           <cell r="B171" t="str">
-            <v>烈酒</v>
+            <v>蛋糕</v>
           </cell>
           <cell r="C171">
-            <v>5</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>401002</v>
+            <v>306001</v>
           </cell>
           <cell r="B172" t="str">
-            <v>果酒</v>
+            <v>蜂蜜</v>
           </cell>
           <cell r="C172">
-            <v>5</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>401003</v>
+            <v>401001</v>
           </cell>
           <cell r="B173" t="str">
-            <v>蜂蜜酒</v>
+            <v>烈酒</v>
           </cell>
           <cell r="C173">
-            <v>6</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>402001</v>
+            <v>401002</v>
           </cell>
           <cell r="B174" t="str">
-            <v>柴火</v>
+            <v>果酒</v>
           </cell>
           <cell r="C174">
-            <v>1</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>403001</v>
+            <v>401003</v>
           </cell>
           <cell r="B175" t="str">
-            <v>普通工具</v>
+            <v>蜂蜜酒</v>
           </cell>
           <cell r="C175">
-            <v>12</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>403002</v>
+            <v>402001</v>
           </cell>
           <cell r="B176" t="str">
-            <v>优质工具</v>
+            <v>柴火</v>
           </cell>
           <cell r="C176">
-            <v>25</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>403003</v>
+            <v>403001</v>
           </cell>
           <cell r="B177" t="str">
-            <v>简单工具</v>
+            <v>普通工具</v>
           </cell>
           <cell r="C177">
-            <v>6</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>404001</v>
+            <v>403002</v>
           </cell>
           <cell r="B178" t="str">
-            <v>皮夹克</v>
+            <v>优质工具</v>
           </cell>
           <cell r="C178">
-            <v>5</v>
+            <v>25</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>404002</v>
+            <v>403003</v>
           </cell>
           <cell r="B179" t="str">
-            <v>羊毛衫</v>
+            <v>简单工具</v>
           </cell>
           <cell r="C179">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>404003</v>
+            <v>404001</v>
           </cell>
           <cell r="B180" t="str">
-            <v>保暖衣</v>
+            <v>皮夹克</v>
           </cell>
           <cell r="C180">
-            <v>10</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>409003</v>
+            <v>404002</v>
           </cell>
           <cell r="B181" t="str">
-            <v>战车</v>
+            <v>羊毛衫</v>
           </cell>
           <cell r="C181">
-            <v>180</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>410001</v>
+            <v>404003</v>
           </cell>
           <cell r="B182" t="str">
-            <v>钢铁之心</v>
+            <v>保暖衣</v>
           </cell>
           <cell r="C182">
-            <v>99999999</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>410002</v>
+            <v>409003</v>
           </cell>
           <cell r="B183" t="str">
-            <v>熔岩之心</v>
+            <v>战车</v>
           </cell>
           <cell r="C183">
-            <v>99999999</v>
+            <v>180</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>410003</v>
+            <v>410001</v>
           </cell>
           <cell r="B184" t="str">
-            <v>寒冰之心</v>
+            <v>钢铁之心</v>
           </cell>
           <cell r="C184">
             <v>99999999</v>
@@ -3085,10 +3161,10 @@
         </row>
         <row r="185">
           <cell r="A185">
-            <v>410004</v>
+            <v>410002</v>
           </cell>
           <cell r="B185" t="str">
-            <v>森林之心</v>
+            <v>熔岩之心</v>
           </cell>
           <cell r="C185">
             <v>99999999</v>
@@ -3096,32 +3172,32 @@
         </row>
         <row r="186">
           <cell r="A186">
-            <v>412001</v>
+            <v>410003</v>
           </cell>
           <cell r="B186" t="str">
-            <v>咖啡</v>
+            <v>寒冰之心</v>
           </cell>
           <cell r="C186">
-            <v>10</v>
+            <v>99999999</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>412002</v>
+            <v>410004</v>
           </cell>
           <cell r="B187" t="str">
-            <v>巧克力</v>
+            <v>森林之心</v>
           </cell>
           <cell r="C187">
-            <v>10</v>
+            <v>99999999</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>412003</v>
+            <v>412001</v>
           </cell>
           <cell r="B188" t="str">
-            <v>糖</v>
+            <v>咖啡</v>
           </cell>
           <cell r="C188">
             <v>10</v>
@@ -3129,10 +3205,10 @@
         </row>
         <row r="189">
           <cell r="A189">
-            <v>413001</v>
+            <v>412002</v>
           </cell>
           <cell r="B189" t="str">
-            <v>简单武器</v>
+            <v>巧克力</v>
           </cell>
           <cell r="C189">
             <v>10</v>
@@ -3140,736 +3216,736 @@
         </row>
         <row r="190">
           <cell r="A190">
-            <v>413002</v>
+            <v>412003</v>
           </cell>
           <cell r="B190" t="str">
-            <v>普通武器</v>
+            <v>糖</v>
           </cell>
           <cell r="C190">
-            <v>50</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>413003</v>
+            <v>413001</v>
           </cell>
           <cell r="B191" t="str">
-            <v>优良武器</v>
+            <v>简单武器</v>
           </cell>
           <cell r="C191">
-            <v>150</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>413004</v>
+            <v>413002</v>
           </cell>
           <cell r="B192" t="str">
-            <v>高级武器</v>
+            <v>普通武器</v>
           </cell>
           <cell r="C192">
-            <v>400</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>413005</v>
+            <v>413003</v>
           </cell>
           <cell r="B193" t="str">
-            <v>稀有武器</v>
+            <v>优良武器</v>
           </cell>
           <cell r="C193">
-            <v>2000</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>413006</v>
+            <v>413004</v>
           </cell>
           <cell r="B194" t="str">
-            <v>特殊武器</v>
+            <v>高级武器</v>
           </cell>
           <cell r="C194">
-            <v>4500</v>
+            <v>400</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>413007</v>
+            <v>413005</v>
           </cell>
           <cell r="B195" t="str">
-            <v>极品武器</v>
+            <v>稀有武器</v>
           </cell>
           <cell r="C195">
-            <v>15000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>413008</v>
+            <v>413006</v>
           </cell>
           <cell r="B196" t="str">
-            <v>传说武器</v>
+            <v>特殊武器</v>
           </cell>
           <cell r="C196">
-            <v>40000</v>
+            <v>4500</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>413009</v>
+            <v>413007</v>
           </cell>
           <cell r="B197" t="str">
-            <v>史诗武器</v>
+            <v>极品武器</v>
           </cell>
           <cell r="C197">
-            <v>88888</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>414001</v>
+            <v>413008</v>
           </cell>
           <cell r="B198" t="str">
-            <v>简单盾牌</v>
+            <v>传说武器</v>
           </cell>
           <cell r="C198">
-            <v>10</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>414002</v>
+            <v>413009</v>
           </cell>
           <cell r="B199" t="str">
-            <v>普通盾牌</v>
+            <v>史诗武器</v>
           </cell>
           <cell r="C199">
-            <v>50</v>
+            <v>88888</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>414003</v>
+            <v>414001</v>
           </cell>
           <cell r="B200" t="str">
-            <v>优良盾牌</v>
+            <v>简单盾牌</v>
           </cell>
           <cell r="C200">
-            <v>150</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>414004</v>
+            <v>414002</v>
           </cell>
           <cell r="B201" t="str">
-            <v>高级盾牌</v>
+            <v>普通盾牌</v>
           </cell>
           <cell r="C201">
-            <v>400</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>414005</v>
+            <v>414003</v>
           </cell>
           <cell r="B202" t="str">
-            <v>稀有盾牌</v>
+            <v>优良盾牌</v>
           </cell>
           <cell r="C202">
-            <v>2000</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>414006</v>
+            <v>414004</v>
           </cell>
           <cell r="B203" t="str">
-            <v>特殊盾牌</v>
+            <v>高级盾牌</v>
           </cell>
           <cell r="C203">
-            <v>4500</v>
+            <v>400</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>414007</v>
+            <v>414005</v>
           </cell>
           <cell r="B204" t="str">
-            <v>极品盾牌</v>
+            <v>稀有盾牌</v>
           </cell>
           <cell r="C204">
-            <v>15000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>414008</v>
+            <v>414006</v>
           </cell>
           <cell r="B205" t="str">
-            <v>传说盾牌</v>
+            <v>特殊盾牌</v>
           </cell>
           <cell r="C205">
-            <v>40000</v>
+            <v>4500</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>414009</v>
+            <v>414007</v>
           </cell>
           <cell r="B206" t="str">
-            <v>史诗盾牌</v>
+            <v>极品盾牌</v>
           </cell>
           <cell r="C206">
-            <v>88888</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>415001</v>
+            <v>414008</v>
           </cell>
           <cell r="B207" t="str">
-            <v>简单盔甲</v>
+            <v>传说盾牌</v>
           </cell>
           <cell r="C207">
-            <v>10</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>415002</v>
+            <v>414009</v>
           </cell>
           <cell r="B208" t="str">
-            <v>普通盔甲</v>
+            <v>史诗盾牌</v>
           </cell>
           <cell r="C208">
-            <v>50</v>
+            <v>88888</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>415003</v>
+            <v>415001</v>
           </cell>
           <cell r="B209" t="str">
-            <v>优良盔甲</v>
+            <v>简单盔甲</v>
           </cell>
           <cell r="C209">
-            <v>150</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>415004</v>
+            <v>415002</v>
           </cell>
           <cell r="B210" t="str">
-            <v>高级盔甲</v>
+            <v>普通盔甲</v>
           </cell>
           <cell r="C210">
-            <v>400</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>415005</v>
+            <v>415003</v>
           </cell>
           <cell r="B211" t="str">
-            <v>稀有盔甲</v>
+            <v>优良盔甲</v>
           </cell>
           <cell r="C211">
-            <v>2000</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>415006</v>
+            <v>415004</v>
           </cell>
           <cell r="B212" t="str">
-            <v>特殊盔甲</v>
+            <v>高级盔甲</v>
           </cell>
           <cell r="C212">
-            <v>4500</v>
+            <v>400</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>415007</v>
+            <v>415005</v>
           </cell>
           <cell r="B213" t="str">
-            <v>极品盔甲</v>
+            <v>稀有盔甲</v>
           </cell>
           <cell r="C213">
-            <v>15000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>415008</v>
+            <v>415006</v>
           </cell>
           <cell r="B214" t="str">
-            <v>传说盔甲</v>
+            <v>特殊盔甲</v>
           </cell>
           <cell r="C214">
-            <v>40000</v>
+            <v>4500</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>415009</v>
+            <v>415007</v>
           </cell>
           <cell r="B215" t="str">
-            <v>史诗盔甲</v>
+            <v>极品盔甲</v>
           </cell>
           <cell r="C215">
-            <v>88888</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>416001</v>
+            <v>415008</v>
           </cell>
           <cell r="B216" t="str">
-            <v>两轮马车</v>
+            <v>传说盔甲</v>
           </cell>
           <cell r="C216">
-            <v>1000</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>416002</v>
+            <v>415009</v>
           </cell>
           <cell r="B217" t="str">
-            <v>四轮马车</v>
+            <v>史诗盔甲</v>
           </cell>
           <cell r="C217">
-            <v>2000</v>
+            <v>88888</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>417001</v>
+            <v>416001</v>
           </cell>
           <cell r="B218" t="str">
-            <v>损坏的简单武器</v>
+            <v>两轮马车</v>
           </cell>
           <cell r="C218">
-            <v>5</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>417002</v>
+            <v>416002</v>
           </cell>
           <cell r="B219" t="str">
-            <v>损坏的普通武器</v>
+            <v>四轮马车</v>
           </cell>
           <cell r="C219">
-            <v>10</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>417003</v>
+            <v>417001</v>
           </cell>
           <cell r="B220" t="str">
-            <v>损坏的优良武器</v>
+            <v>损坏的简单武器</v>
           </cell>
           <cell r="C220">
-            <v>15</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>417004</v>
+            <v>417002</v>
           </cell>
           <cell r="B221" t="str">
-            <v>损坏的高级武器</v>
+            <v>损坏的普通武器</v>
           </cell>
           <cell r="C221">
-            <v>20</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>417005</v>
+            <v>417003</v>
           </cell>
           <cell r="B222" t="str">
-            <v>损坏的稀有武器</v>
+            <v>损坏的优良武器</v>
           </cell>
           <cell r="C222">
-            <v>600</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>417006</v>
+            <v>417004</v>
           </cell>
           <cell r="B223" t="str">
-            <v>损坏的特殊武器</v>
+            <v>损坏的高级武器</v>
           </cell>
           <cell r="C223">
-            <v>1800</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>417007</v>
+            <v>417005</v>
           </cell>
           <cell r="B224" t="str">
-            <v>损坏的极品武器</v>
+            <v>损坏的稀有武器</v>
           </cell>
           <cell r="C224">
-            <v>6000</v>
+            <v>600</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>417008</v>
+            <v>417006</v>
           </cell>
           <cell r="B225" t="str">
-            <v>损坏的传说武器</v>
+            <v>损坏的特殊武器</v>
           </cell>
           <cell r="C225">
-            <v>15000</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>417009</v>
+            <v>417007</v>
           </cell>
           <cell r="B226" t="str">
-            <v>损坏的史诗武器</v>
+            <v>损坏的极品武器</v>
           </cell>
           <cell r="C226">
-            <v>30000</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>417010</v>
+            <v>417008</v>
           </cell>
           <cell r="B227" t="str">
-            <v>损坏的简单盾牌</v>
+            <v>损坏的传说武器</v>
           </cell>
           <cell r="C227">
-            <v>5</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>417011</v>
+            <v>417009</v>
           </cell>
           <cell r="B228" t="str">
-            <v>损坏的普通盾牌</v>
+            <v>损坏的史诗武器</v>
           </cell>
           <cell r="C228">
-            <v>10</v>
+            <v>30000</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>417012</v>
+            <v>417010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>损坏的优良盾牌</v>
+            <v>损坏的简单盾牌</v>
           </cell>
           <cell r="C229">
-            <v>15</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>417013</v>
+            <v>417011</v>
           </cell>
           <cell r="B230" t="str">
-            <v>损坏的高级盾牌</v>
+            <v>损坏的普通盾牌</v>
           </cell>
           <cell r="C230">
-            <v>20</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>417014</v>
+            <v>417012</v>
           </cell>
           <cell r="B231" t="str">
-            <v>损坏的稀有盾牌</v>
+            <v>损坏的优良盾牌</v>
           </cell>
           <cell r="C231">
-            <v>600</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>417015</v>
+            <v>417013</v>
           </cell>
           <cell r="B232" t="str">
-            <v>损坏的特殊盾牌</v>
+            <v>损坏的高级盾牌</v>
           </cell>
           <cell r="C232">
-            <v>1800</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>417016</v>
+            <v>417014</v>
           </cell>
           <cell r="B233" t="str">
-            <v>损坏的极品盾牌</v>
+            <v>损坏的稀有盾牌</v>
           </cell>
           <cell r="C233">
-            <v>6000</v>
+            <v>600</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>417017</v>
+            <v>417015</v>
           </cell>
           <cell r="B234" t="str">
-            <v>损坏的传说盾牌</v>
+            <v>损坏的特殊盾牌</v>
           </cell>
           <cell r="C234">
-            <v>15000</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>417018</v>
+            <v>417016</v>
           </cell>
           <cell r="B235" t="str">
-            <v>损坏的史诗盾牌</v>
+            <v>损坏的极品盾牌</v>
           </cell>
           <cell r="C235">
-            <v>30000</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>417019</v>
+            <v>417017</v>
           </cell>
           <cell r="B236" t="str">
-            <v>损坏的简单盔甲</v>
+            <v>损坏的传说盾牌</v>
           </cell>
           <cell r="C236">
-            <v>5</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>417020</v>
+            <v>417018</v>
           </cell>
           <cell r="B237" t="str">
-            <v>损坏的普通盔甲</v>
+            <v>损坏的史诗盾牌</v>
           </cell>
           <cell r="C237">
-            <v>10</v>
+            <v>30000</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>417021</v>
+            <v>417019</v>
           </cell>
           <cell r="B238" t="str">
-            <v>损坏的优良盔甲</v>
+            <v>损坏的简单盔甲</v>
           </cell>
           <cell r="C238">
-            <v>15</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>417022</v>
+            <v>417020</v>
           </cell>
           <cell r="B239" t="str">
-            <v>损坏的高级盔甲</v>
+            <v>损坏的普通盔甲</v>
           </cell>
           <cell r="C239">
-            <v>20</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>417023</v>
+            <v>417021</v>
           </cell>
           <cell r="B240" t="str">
-            <v>损坏的稀有盔甲</v>
+            <v>损坏的优良盔甲</v>
           </cell>
           <cell r="C240">
-            <v>600</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>417024</v>
+            <v>417022</v>
           </cell>
           <cell r="B241" t="str">
-            <v>损坏的特殊盔甲</v>
+            <v>损坏的高级盔甲</v>
           </cell>
           <cell r="C241">
-            <v>1800</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>417025</v>
+            <v>417023</v>
           </cell>
           <cell r="B242" t="str">
-            <v>损坏的极品盔甲</v>
+            <v>损坏的稀有盔甲</v>
           </cell>
           <cell r="C242">
-            <v>6000</v>
+            <v>600</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>417026</v>
+            <v>417024</v>
           </cell>
           <cell r="B243" t="str">
-            <v>损坏的传说盔甲</v>
+            <v>损坏的特殊盔甲</v>
           </cell>
           <cell r="C243">
-            <v>15000</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>417027</v>
+            <v>417025</v>
           </cell>
           <cell r="B244" t="str">
-            <v>损坏的史诗盔甲</v>
+            <v>损坏的极品盔甲</v>
           </cell>
           <cell r="C244">
-            <v>30000</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>418001</v>
+            <v>417026</v>
           </cell>
           <cell r="B245" t="str">
-            <v>蘑菇精华</v>
+            <v>损坏的传说盔甲</v>
           </cell>
           <cell r="C245">
-            <v>500</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>418002</v>
+            <v>417027</v>
           </cell>
           <cell r="B246" t="str">
-            <v>养颜丹</v>
+            <v>损坏的史诗盔甲</v>
           </cell>
           <cell r="C246">
-            <v>1000</v>
+            <v>30000</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>419001</v>
+            <v>418001</v>
           </cell>
           <cell r="B247" t="str">
-            <v>雨伞</v>
+            <v>蘑菇精华</v>
           </cell>
           <cell r="C247">
-            <v>5</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>420001</v>
+            <v>418002</v>
           </cell>
           <cell r="B248" t="str">
-            <v>皮包</v>
+            <v>养颜丹</v>
           </cell>
           <cell r="C248">
-            <v>5</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>421001</v>
+            <v>419001</v>
           </cell>
           <cell r="B249" t="str">
-            <v>药茶</v>
+            <v>雨伞</v>
           </cell>
           <cell r="C249">
-            <v>10</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>422001</v>
+            <v>420001</v>
           </cell>
           <cell r="B250" t="str">
-            <v>火药</v>
+            <v>皮包</v>
           </cell>
           <cell r="C250">
-            <v>100</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>423001</v>
+            <v>421001</v>
           </cell>
           <cell r="B251" t="str">
-            <v>榴弹</v>
+            <v>药茶</v>
           </cell>
           <cell r="C251">
-            <v>500</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>423002</v>
+            <v>422001</v>
           </cell>
           <cell r="B252" t="str">
-            <v>铁弹</v>
+            <v>火药</v>
           </cell>
           <cell r="C252">
-            <v>500</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>423003</v>
+            <v>423001</v>
           </cell>
           <cell r="B253" t="str">
-            <v>巨型炸弹</v>
+            <v>榴弹</v>
           </cell>
           <cell r="C253">
-            <v>5000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>424001</v>
+            <v>423002</v>
           </cell>
           <cell r="B254" t="str">
-            <v>人伦书</v>
+            <v>铁弹</v>
           </cell>
           <cell r="C254">
-            <v>1000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>424002</v>
+            <v>423003</v>
           </cell>
           <cell r="B255" t="str">
-            <v>轮回书</v>
+            <v>巨型炸弹</v>
           </cell>
           <cell r="C255">
-            <v>1000</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>424003</v>
+            <v>424001</v>
           </cell>
           <cell r="B256" t="str">
-            <v>天职书</v>
+            <v>人伦书</v>
           </cell>
           <cell r="C256">
             <v>1000</v>
@@ -3877,10 +3953,10 @@
         </row>
         <row r="257">
           <cell r="A257">
-            <v>424004</v>
+            <v>424002</v>
           </cell>
           <cell r="B257" t="str">
-            <v>兵法书</v>
+            <v>轮回书</v>
           </cell>
           <cell r="C257">
             <v>1000</v>
@@ -3888,10 +3964,10 @@
         </row>
         <row r="258">
           <cell r="A258">
-            <v>424005</v>
+            <v>424003</v>
           </cell>
           <cell r="B258" t="str">
-            <v>管理书</v>
+            <v>天职书</v>
           </cell>
           <cell r="C258">
             <v>1000</v>
@@ -3899,10 +3975,10 @@
         </row>
         <row r="259">
           <cell r="A259">
-            <v>424006</v>
+            <v>424004</v>
           </cell>
           <cell r="B259" t="str">
-            <v>忠义书</v>
+            <v>兵法书</v>
           </cell>
           <cell r="C259">
             <v>1000</v>
@@ -3910,109 +3986,109 @@
         </row>
         <row r="260">
           <cell r="A260">
-            <v>424007</v>
+            <v>424005</v>
           </cell>
           <cell r="B260" t="str">
-            <v>启蒙书</v>
+            <v>管理书</v>
           </cell>
           <cell r="C260">
-            <v>150</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>424008</v>
+            <v>424006</v>
           </cell>
           <cell r="B261" t="str">
-            <v>心灵书</v>
+            <v>忠义书</v>
           </cell>
           <cell r="C261">
-            <v>50</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>425001</v>
+            <v>424007</v>
           </cell>
           <cell r="B262" t="str">
-            <v>炸弹果</v>
+            <v>启蒙书</v>
           </cell>
           <cell r="C262">
-            <v>0</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>425002</v>
+            <v>424008</v>
           </cell>
           <cell r="B263" t="str">
-            <v>精英炸弹果</v>
+            <v>心灵书</v>
           </cell>
           <cell r="C263">
-            <v>0</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>426001</v>
+            <v>425001</v>
           </cell>
           <cell r="B264" t="str">
-            <v>魔法戒指</v>
+            <v>炸弹果</v>
           </cell>
           <cell r="C264">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>427001</v>
+            <v>425002</v>
           </cell>
           <cell r="B265" t="str">
-            <v>魔法项链</v>
+            <v>精英炸弹果</v>
           </cell>
           <cell r="C265">
-            <v>2500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>428001</v>
+            <v>426001</v>
           </cell>
           <cell r="B266" t="str">
-            <v>子弹</v>
+            <v>魔法戒指</v>
           </cell>
           <cell r="C266">
-            <v>70</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>429001</v>
+            <v>427001</v>
           </cell>
           <cell r="B267" t="str">
-            <v>动物生长素</v>
+            <v>魔法项链</v>
           </cell>
           <cell r="C267">
-            <v>10</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>429002</v>
+            <v>428001</v>
           </cell>
           <cell r="B268" t="str">
-            <v xml:space="preserve">动物促产素 </v>
+            <v>子弹</v>
           </cell>
           <cell r="C268">
-            <v>10</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>429003</v>
+            <v>429001</v>
           </cell>
           <cell r="B269" t="str">
-            <v>动物催肥素</v>
+            <v>动物生长素</v>
           </cell>
           <cell r="C269">
             <v>10</v>
@@ -4020,120 +4096,120 @@
         </row>
         <row r="270">
           <cell r="A270">
-            <v>430001</v>
+            <v>429002</v>
           </cell>
           <cell r="B270" t="str">
-            <v>国王之冠</v>
+            <v xml:space="preserve">动物促产素 </v>
           </cell>
           <cell r="C270">
-            <v>999999</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>430002</v>
+            <v>429003</v>
           </cell>
           <cell r="B271" t="str">
-            <v>驭龙瓶</v>
+            <v>动物催肥素</v>
           </cell>
           <cell r="C271">
-            <v>999999</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>501001</v>
+            <v>430001</v>
           </cell>
           <cell r="B272" t="str">
-            <v>鸡</v>
+            <v>国王之冠</v>
           </cell>
           <cell r="C272">
-            <v>500</v>
+            <v>999999</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>501002</v>
+            <v>430002</v>
           </cell>
           <cell r="B273" t="str">
-            <v>羊</v>
+            <v>驭龙瓶</v>
           </cell>
           <cell r="C273">
-            <v>1000</v>
+            <v>999999</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>501003</v>
+            <v>501001</v>
           </cell>
           <cell r="B274" t="str">
-            <v>牛</v>
+            <v>鸡</v>
           </cell>
           <cell r="C274">
-            <v>800</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>501004</v>
+            <v>501002</v>
           </cell>
           <cell r="B275" t="str">
-            <v>马</v>
+            <v>羊</v>
           </cell>
           <cell r="C275">
-            <v>1000</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>501005</v>
+            <v>501003</v>
           </cell>
           <cell r="B276" t="str">
-            <v>猪</v>
+            <v>牛</v>
           </cell>
           <cell r="C276">
-            <v>800</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>501006</v>
+            <v>501004</v>
           </cell>
           <cell r="B277" t="str">
-            <v>驯狼</v>
+            <v>马</v>
           </cell>
           <cell r="C277">
-            <v>800</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>502001</v>
+            <v>501005</v>
           </cell>
           <cell r="B278" t="str">
-            <v>鹿</v>
+            <v>猪</v>
           </cell>
           <cell r="C278">
-            <v>1000</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>502002</v>
+            <v>501006</v>
           </cell>
           <cell r="B279" t="str">
-            <v>野马</v>
+            <v>驯狼</v>
           </cell>
           <cell r="C279">
-            <v>1000</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>502003</v>
+            <v>502001</v>
           </cell>
           <cell r="B280" t="str">
-            <v>野猪</v>
+            <v>鹿</v>
           </cell>
           <cell r="C280">
             <v>1000</v>
@@ -4141,10 +4217,10 @@
         </row>
         <row r="281">
           <cell r="A281">
-            <v>502004</v>
+            <v>502002</v>
           </cell>
           <cell r="B281" t="str">
-            <v>野狼</v>
+            <v>野马</v>
           </cell>
           <cell r="C281">
             <v>1000</v>
@@ -4152,10 +4228,10 @@
         </row>
         <row r="282">
           <cell r="A282">
-            <v>502005</v>
+            <v>502003</v>
           </cell>
           <cell r="B282" t="str">
-            <v>白鹿</v>
+            <v>野猪</v>
           </cell>
           <cell r="C282">
             <v>1000</v>
@@ -4163,10 +4239,10 @@
         </row>
         <row r="283">
           <cell r="A283">
-            <v>502006</v>
+            <v>502004</v>
           </cell>
           <cell r="B283" t="str">
-            <v>梅花鹿</v>
+            <v>野狼</v>
           </cell>
           <cell r="C283">
             <v>1000</v>
@@ -4174,10 +4250,10 @@
         </row>
         <row r="284">
           <cell r="A284">
-            <v>503001</v>
+            <v>502005</v>
           </cell>
           <cell r="B284" t="str">
-            <v>猫</v>
+            <v>白鹿</v>
           </cell>
           <cell r="C284">
             <v>1000</v>
@@ -4185,10 +4261,10 @@
         </row>
         <row r="285">
           <cell r="A285">
-            <v>504001</v>
+            <v>502006</v>
           </cell>
           <cell r="B285" t="str">
-            <v>战马</v>
+            <v>梅花鹿</v>
           </cell>
           <cell r="C285">
             <v>1000</v>
@@ -4196,10 +4272,10 @@
         </row>
         <row r="286">
           <cell r="A286">
-            <v>504002</v>
+            <v>503001</v>
           </cell>
           <cell r="B286" t="str">
-            <v>战猪</v>
+            <v>猫</v>
           </cell>
           <cell r="C286">
             <v>1000</v>
@@ -4207,10 +4283,10 @@
         </row>
         <row r="287">
           <cell r="A287">
-            <v>504003</v>
+            <v>504001</v>
           </cell>
           <cell r="B287" t="str">
-            <v>战狼</v>
+            <v>战马</v>
           </cell>
           <cell r="C287">
             <v>1000</v>
@@ -4218,10 +4294,10 @@
         </row>
         <row r="288">
           <cell r="A288">
-            <v>504004</v>
+            <v>504002</v>
           </cell>
           <cell r="B288" t="str">
-            <v>马坐骑</v>
+            <v>战猪</v>
           </cell>
           <cell r="C288">
             <v>1000</v>
@@ -4229,10 +4305,10 @@
         </row>
         <row r="289">
           <cell r="A289">
-            <v>504005</v>
+            <v>504003</v>
           </cell>
           <cell r="B289" t="str">
-            <v>猪坐骑</v>
+            <v>战狼</v>
           </cell>
           <cell r="C289">
             <v>1000</v>
@@ -4240,10 +4316,10 @@
         </row>
         <row r="290">
           <cell r="A290">
-            <v>504006</v>
+            <v>504004</v>
           </cell>
           <cell r="B290" t="str">
-            <v>狼坐骑</v>
+            <v>马坐骑</v>
           </cell>
           <cell r="C290">
             <v>1000</v>
@@ -4251,10 +4327,10 @@
         </row>
         <row r="291">
           <cell r="A291">
-            <v>504007</v>
+            <v>504005</v>
           </cell>
           <cell r="B291" t="str">
-            <v>骑士马坐骑</v>
+            <v>猪坐骑</v>
           </cell>
           <cell r="C291">
             <v>1000</v>
@@ -4262,10 +4338,10 @@
         </row>
         <row r="292">
           <cell r="A292">
-            <v>504008</v>
+            <v>504006</v>
           </cell>
           <cell r="B292" t="str">
-            <v>领主马坐骑</v>
+            <v>狼坐骑</v>
           </cell>
           <cell r="C292">
             <v>1000</v>
@@ -4273,10 +4349,10 @@
         </row>
         <row r="293">
           <cell r="A293">
-            <v>504009</v>
+            <v>504007</v>
           </cell>
           <cell r="B293" t="str">
-            <v>皇家骑士坐骑</v>
+            <v>骑士马坐骑</v>
           </cell>
           <cell r="C293">
             <v>1000</v>
@@ -4284,98 +4360,98 @@
         </row>
         <row r="294">
           <cell r="A294">
-            <v>601001</v>
+            <v>504008</v>
           </cell>
           <cell r="B294" t="str">
-            <v>煤</v>
+            <v>领主马坐骑</v>
           </cell>
           <cell r="C294">
-            <v>5</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>602001</v>
+            <v>504009</v>
           </cell>
           <cell r="B295" t="str">
-            <v>草药</v>
+            <v>皇家骑士坐骑</v>
           </cell>
           <cell r="C295">
-            <v>5</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>602002</v>
+            <v>601001</v>
           </cell>
           <cell r="B296" t="str">
-            <v>生命药水</v>
+            <v>煤</v>
           </cell>
           <cell r="C296">
-            <v>15</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>602003</v>
+            <v>602001</v>
           </cell>
           <cell r="B297" t="str">
-            <v>生命果实</v>
+            <v>草药</v>
           </cell>
           <cell r="C297">
-            <v>50</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>602004</v>
+            <v>602002</v>
           </cell>
           <cell r="B298" t="str">
-            <v>忘忧果</v>
+            <v>生命药水</v>
           </cell>
           <cell r="C298">
-            <v>50</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>603001</v>
+            <v>602003</v>
           </cell>
           <cell r="B299" t="str">
-            <v>铁锭</v>
+            <v>生命果实</v>
           </cell>
           <cell r="C299">
-            <v>5</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>603002</v>
+            <v>602004</v>
           </cell>
           <cell r="B300" t="str">
-            <v>秘银锭</v>
+            <v>忘忧果</v>
           </cell>
           <cell r="C300">
-            <v>100</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>603003</v>
+            <v>603001</v>
           </cell>
           <cell r="B301" t="str">
-            <v>精金锭</v>
+            <v>铁锭</v>
           </cell>
           <cell r="C301">
-            <v>100</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>603004</v>
+            <v>603002</v>
           </cell>
           <cell r="B302" t="str">
-            <v>山铜锭</v>
+            <v>秘银锭</v>
           </cell>
           <cell r="C302">
             <v>100</v>
@@ -4383,109 +4459,109 @@
         </row>
         <row r="303">
           <cell r="A303">
-            <v>604001</v>
+            <v>603003</v>
           </cell>
           <cell r="B303" t="str">
-            <v>原木</v>
+            <v>精金锭</v>
           </cell>
           <cell r="C303">
-            <v>2</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>605001</v>
+            <v>603004</v>
           </cell>
           <cell r="B304" t="str">
-            <v>石料</v>
+            <v>山铜锭</v>
           </cell>
           <cell r="C304">
-            <v>4</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>606001</v>
+            <v>604001</v>
           </cell>
           <cell r="B305" t="str">
-            <v>皮革</v>
+            <v>原木</v>
           </cell>
           <cell r="C305">
-            <v>3</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>606002</v>
+            <v>605001</v>
           </cell>
           <cell r="B306" t="str">
-            <v>羊毛</v>
+            <v>石料</v>
           </cell>
           <cell r="C306">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>607001</v>
+            <v>606001</v>
           </cell>
           <cell r="B307" t="str">
-            <v>白银</v>
+            <v>皮革</v>
           </cell>
           <cell r="C307">
-            <v>100</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>608001</v>
+            <v>606002</v>
           </cell>
           <cell r="B308" t="str">
-            <v>黄金</v>
+            <v>羊毛</v>
           </cell>
           <cell r="C308">
-            <v>1000</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>609001</v>
+            <v>607001</v>
           </cell>
           <cell r="B309" t="str">
-            <v>肥料</v>
+            <v>白银</v>
           </cell>
           <cell r="C309">
-            <v>1</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>610001</v>
+            <v>608001</v>
           </cell>
           <cell r="B310" t="str">
-            <v>粪便</v>
+            <v>黄金</v>
           </cell>
           <cell r="C310">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>610002</v>
+            <v>609001</v>
           </cell>
           <cell r="B311" t="str">
-            <v>腐败食物</v>
+            <v>肥料</v>
           </cell>
           <cell r="C311">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>610003</v>
+            <v>610001</v>
           </cell>
           <cell r="B312" t="str">
-            <v>灰烬</v>
+            <v>粪便</v>
           </cell>
           <cell r="C312">
             <v>0</v>
@@ -4493,87 +4569,87 @@
         </row>
         <row r="313">
           <cell r="A313">
-            <v>611001</v>
+            <v>610002</v>
           </cell>
           <cell r="B313" t="str">
-            <v>咖啡豆</v>
+            <v>腐败食物</v>
           </cell>
           <cell r="C313">
-            <v>5</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>611002</v>
+            <v>610003</v>
           </cell>
           <cell r="B314" t="str">
-            <v>可可豆</v>
+            <v>灰烬</v>
           </cell>
           <cell r="C314">
-            <v>5</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>611003</v>
+            <v>611001</v>
           </cell>
           <cell r="B315" t="str">
-            <v>甘蔗</v>
+            <v>咖啡豆</v>
           </cell>
           <cell r="C315">
-            <v>1</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>611004</v>
+            <v>611002</v>
           </cell>
           <cell r="B316" t="str">
-            <v>牛奶</v>
+            <v>可可豆</v>
           </cell>
           <cell r="C316">
-            <v>2</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>611005</v>
+            <v>611003</v>
           </cell>
           <cell r="B317" t="str">
-            <v>面粉</v>
+            <v>甘蔗</v>
           </cell>
           <cell r="C317">
-            <v>2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>612001</v>
+            <v>611004</v>
           </cell>
           <cell r="B318" t="str">
-            <v>红宝石</v>
+            <v>牛奶</v>
           </cell>
           <cell r="C318">
-            <v>500</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>612002</v>
+            <v>611005</v>
           </cell>
           <cell r="B319" t="str">
-            <v>蓝宝石</v>
+            <v>面粉</v>
           </cell>
           <cell r="C319">
-            <v>500</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>612003</v>
+            <v>612001</v>
           </cell>
           <cell r="B320" t="str">
-            <v>绿宝石</v>
+            <v>红宝石</v>
           </cell>
           <cell r="C320">
             <v>500</v>
@@ -4581,54 +4657,54 @@
         </row>
         <row r="321">
           <cell r="A321">
-            <v>613001</v>
+            <v>612002</v>
           </cell>
           <cell r="B321" t="str">
-            <v>金蛋</v>
+            <v>蓝宝石</v>
           </cell>
           <cell r="C321">
-            <v>1000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>614001</v>
+            <v>612003</v>
           </cell>
           <cell r="B322" t="str">
-            <v>龙涎香</v>
+            <v>绿宝石</v>
           </cell>
           <cell r="C322">
-            <v>800</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>615001</v>
+            <v>613001</v>
           </cell>
           <cell r="B323" t="str">
-            <v>红宝石碎片</v>
+            <v>金蛋</v>
           </cell>
           <cell r="C323">
-            <v>50</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>615002</v>
+            <v>614001</v>
           </cell>
           <cell r="B324" t="str">
-            <v>蓝宝石碎片</v>
+            <v>龙涎香</v>
           </cell>
           <cell r="C324">
-            <v>50</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>615003</v>
+            <v>615001</v>
           </cell>
           <cell r="B325" t="str">
-            <v>绿宝石碎片</v>
+            <v>红宝石碎片</v>
           </cell>
           <cell r="C325">
             <v>50</v>
@@ -4636,32 +4712,32 @@
         </row>
         <row r="326">
           <cell r="A326">
-            <v>616001</v>
+            <v>615002</v>
           </cell>
           <cell r="B326" t="str">
-            <v>铁矿</v>
+            <v>蓝宝石碎片</v>
           </cell>
           <cell r="C326">
-            <v>2</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>616002</v>
+            <v>615003</v>
           </cell>
           <cell r="B327" t="str">
-            <v>秘银矿</v>
+            <v>绿宝石碎片</v>
           </cell>
           <cell r="C327">
-            <v>2</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>616003</v>
+            <v>616001</v>
           </cell>
           <cell r="B328" t="str">
-            <v>精金矿</v>
+            <v>铁矿</v>
           </cell>
           <cell r="C328">
             <v>2</v>
@@ -4669,10 +4745,10 @@
         </row>
         <row r="329">
           <cell r="A329">
-            <v>616004</v>
+            <v>616002</v>
           </cell>
           <cell r="B329" t="str">
-            <v>山铜矿</v>
+            <v>秘银矿</v>
           </cell>
           <cell r="C329">
             <v>2</v>
@@ -4680,10 +4756,10 @@
         </row>
         <row r="330">
           <cell r="A330">
-            <v>616005</v>
+            <v>616003</v>
           </cell>
           <cell r="B330" t="str">
-            <v>金矿</v>
+            <v>精金矿</v>
           </cell>
           <cell r="C330">
             <v>2</v>
@@ -4691,10 +4767,10 @@
         </row>
         <row r="331">
           <cell r="A331">
-            <v>616006</v>
+            <v>616004</v>
           </cell>
           <cell r="B331" t="str">
-            <v>银矿</v>
+            <v>山铜矿</v>
           </cell>
           <cell r="C331">
             <v>2</v>
@@ -4702,153 +4778,153 @@
         </row>
         <row r="332">
           <cell r="A332">
-            <v>617001</v>
+            <v>616005</v>
           </cell>
           <cell r="B332" t="str">
-            <v>牧草</v>
+            <v>金矿</v>
           </cell>
           <cell r="C332">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>618001</v>
+            <v>616006</v>
           </cell>
           <cell r="B333" t="str">
-            <v>银币</v>
+            <v>银矿</v>
           </cell>
           <cell r="C333">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
-            <v>619001</v>
+            <v>617001</v>
           </cell>
           <cell r="B334" t="str">
-            <v>智慧宝石</v>
+            <v>牧草</v>
           </cell>
           <cell r="C334">
-            <v>1000000</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335">
-            <v>620001</v>
+            <v>618001</v>
           </cell>
           <cell r="B335" t="str">
-            <v>史莱姆凝液</v>
+            <v>银币</v>
           </cell>
           <cell r="C335">
-            <v>50</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336">
-            <v>620002</v>
+            <v>619001</v>
           </cell>
           <cell r="B336" t="str">
-            <v>蚁胶</v>
+            <v>智慧宝石</v>
           </cell>
           <cell r="C336">
-            <v>25</v>
+            <v>1000000</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337">
-            <v>701001</v>
+            <v>620001</v>
           </cell>
           <cell r="B337" t="str">
-            <v>菜豆种子</v>
+            <v>史莱姆凝液</v>
           </cell>
           <cell r="C337">
-            <v>2000</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338">
-            <v>701002</v>
+            <v>620002</v>
           </cell>
           <cell r="B338" t="str">
-            <v>卷心菜种子</v>
+            <v>蚁胶</v>
           </cell>
           <cell r="C338">
-            <v>10000</v>
+            <v>25</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339">
-            <v>701003</v>
+            <v>621001</v>
           </cell>
           <cell r="B339" t="str">
-            <v>辣椒种子</v>
+            <v>白玫瑰</v>
           </cell>
           <cell r="C339">
-            <v>6000</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340">
-            <v>701004</v>
+            <v>621002</v>
           </cell>
           <cell r="B340" t="str">
-            <v>南瓜种子</v>
+            <v>红玫瑰</v>
           </cell>
           <cell r="C340">
-            <v>20000</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341">
-            <v>701005</v>
+            <v>621003</v>
           </cell>
           <cell r="B341" t="str">
-            <v>笋瓜种子</v>
+            <v>蓝玫瑰</v>
           </cell>
           <cell r="C341">
-            <v>4000</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342">
-            <v>702001</v>
+            <v>621004</v>
           </cell>
           <cell r="B342" t="str">
-            <v>玉米种子</v>
+            <v>黄色郁金香</v>
           </cell>
           <cell r="C342">
-            <v>10000</v>
+            <v>40</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343">
-            <v>702002</v>
+            <v>621005</v>
           </cell>
           <cell r="B343" t="str">
-            <v>土豆种子</v>
+            <v>红色郁金香</v>
           </cell>
           <cell r="C343">
-            <v>4000</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344">
-            <v>702003</v>
+            <v>621006</v>
           </cell>
           <cell r="B344" t="str">
-            <v>小麦种子</v>
+            <v>紫色郁金香</v>
           </cell>
           <cell r="C344">
-            <v>2000</v>
+            <v>800</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345">
-            <v>702004</v>
+            <v>701001</v>
           </cell>
           <cell r="B345" t="str">
-            <v>牧草种子</v>
+            <v>菜豆种子</v>
           </cell>
           <cell r="C345">
             <v>2000</v>
@@ -4856,98 +4932,98 @@
         </row>
         <row r="346">
           <cell r="A346">
-            <v>703001</v>
+            <v>701002</v>
           </cell>
           <cell r="B346" t="str">
-            <v>苹果树种子</v>
+            <v>卷心菜种子</v>
           </cell>
           <cell r="C346">
-            <v>2500</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347">
-            <v>703002</v>
+            <v>701003</v>
           </cell>
           <cell r="B347" t="str">
-            <v>樱桃树种子</v>
+            <v>辣椒种子</v>
           </cell>
           <cell r="C347">
-            <v>2500</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348">
-            <v>703004</v>
+            <v>701004</v>
           </cell>
           <cell r="B348" t="str">
-            <v>梨树种子</v>
+            <v>南瓜种子</v>
           </cell>
           <cell r="C348">
-            <v>2500</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349">
-            <v>703006</v>
+            <v>701005</v>
           </cell>
           <cell r="B349" t="str">
-            <v>梅子树种子</v>
+            <v>笋瓜种子</v>
           </cell>
           <cell r="C349">
-            <v>2500</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350">
-            <v>703007</v>
+            <v>702001</v>
           </cell>
           <cell r="B350" t="str">
-            <v>核桃树种子</v>
+            <v>玉米种子</v>
           </cell>
           <cell r="C350">
-            <v>2500</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351">
-            <v>704001</v>
+            <v>702002</v>
           </cell>
           <cell r="B351" t="str">
-            <v>蓝十字花</v>
+            <v>土豆种子</v>
           </cell>
           <cell r="C351">
-            <v>2500</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352">
-            <v>704002</v>
+            <v>702003</v>
           </cell>
           <cell r="B352" t="str">
-            <v>红十字花</v>
+            <v>小麦种子</v>
           </cell>
           <cell r="C352">
-            <v>2500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353">
-            <v>704003</v>
+            <v>702004</v>
           </cell>
           <cell r="B353" t="str">
-            <v>牡丹花</v>
+            <v>牧草种子</v>
           </cell>
           <cell r="C353">
-            <v>2500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354">
-            <v>704004</v>
+            <v>703001</v>
           </cell>
           <cell r="B354" t="str">
-            <v>黄钻花</v>
+            <v>苹果树种子</v>
           </cell>
           <cell r="C354">
             <v>2500</v>
@@ -4955,10 +5031,10 @@
         </row>
         <row r="355">
           <cell r="A355">
-            <v>704005</v>
+            <v>703002</v>
           </cell>
           <cell r="B355" t="str">
-            <v>蓝钻花</v>
+            <v>樱桃树种子</v>
           </cell>
           <cell r="C355">
             <v>2500</v>
@@ -4966,10 +5042,10 @@
         </row>
         <row r="356">
           <cell r="A356">
-            <v>704006</v>
+            <v>703004</v>
           </cell>
           <cell r="B356" t="str">
-            <v>风铃花</v>
+            <v>梨树种子</v>
           </cell>
           <cell r="C356">
             <v>2500</v>
@@ -4977,10 +5053,10 @@
         </row>
         <row r="357">
           <cell r="A357">
-            <v>704007</v>
+            <v>703006</v>
           </cell>
           <cell r="B357" t="str">
-            <v>百合花</v>
+            <v>梅子树种子</v>
           </cell>
           <cell r="C357">
             <v>2500</v>
@@ -4988,10 +5064,10 @@
         </row>
         <row r="358">
           <cell r="A358">
-            <v>704008</v>
+            <v>703007</v>
           </cell>
           <cell r="B358" t="str">
-            <v>杜鹃花</v>
+            <v>核桃树种子</v>
           </cell>
           <cell r="C358">
             <v>2500</v>
@@ -4999,43 +5075,43 @@
         </row>
         <row r="359">
           <cell r="A359">
-            <v>704009</v>
+            <v>704001</v>
           </cell>
           <cell r="B359" t="str">
-            <v>四季玫瑰</v>
+            <v>蓝星花</v>
           </cell>
           <cell r="C359">
-            <v>5000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360">
-            <v>704010</v>
+            <v>704002</v>
           </cell>
           <cell r="B360" t="str">
-            <v>生命之花</v>
+            <v>紫绒花</v>
           </cell>
           <cell r="C360">
-            <v>5000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361">
-            <v>704011</v>
+            <v>704003</v>
           </cell>
           <cell r="B361" t="str">
-            <v>忘忧草</v>
+            <v>红芯菊</v>
           </cell>
           <cell r="C361">
-            <v>5000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362">
-            <v>704012</v>
+            <v>704004</v>
           </cell>
           <cell r="B362" t="str">
-            <v>夏日浆果</v>
+            <v>青铃花</v>
           </cell>
           <cell r="C362">
             <v>2500</v>
@@ -5043,10 +5119,10 @@
         </row>
         <row r="363">
           <cell r="A363">
-            <v>704013</v>
+            <v>704005</v>
           </cell>
           <cell r="B363" t="str">
-            <v>秋日浆果</v>
+            <v>幻彩花</v>
           </cell>
           <cell r="C363">
             <v>2500</v>
@@ -5054,10 +5130,10 @@
         </row>
         <row r="364">
           <cell r="A364">
-            <v>704014</v>
+            <v>704006</v>
           </cell>
           <cell r="B364" t="str">
-            <v>冬日浆果</v>
+            <v>晴雨花</v>
           </cell>
           <cell r="C364">
             <v>2500</v>
@@ -5065,10 +5141,10 @@
         </row>
         <row r="365">
           <cell r="A365">
-            <v>704015</v>
+            <v>704007</v>
           </cell>
           <cell r="B365" t="str">
-            <v>樟树</v>
+            <v>金盏花</v>
           </cell>
           <cell r="C365">
             <v>2500</v>
@@ -5076,10 +5152,10 @@
         </row>
         <row r="366">
           <cell r="A366">
-            <v>704016</v>
+            <v>704008</v>
           </cell>
           <cell r="B366" t="str">
-            <v>榕树</v>
+            <v>玫瑰姫</v>
           </cell>
           <cell r="C366">
             <v>2500</v>
@@ -5087,43 +5163,43 @@
         </row>
         <row r="367">
           <cell r="A367">
-            <v>704017</v>
+            <v>704009</v>
           </cell>
           <cell r="B367" t="str">
-            <v>梧桐</v>
+            <v>月季花</v>
           </cell>
           <cell r="C367">
-            <v>2500</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368">
-            <v>704018</v>
+            <v>704010</v>
           </cell>
           <cell r="B368" t="str">
-            <v>松树</v>
+            <v>生命之花</v>
           </cell>
           <cell r="C368">
-            <v>2500</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369">
-            <v>704019</v>
+            <v>704011</v>
           </cell>
           <cell r="B369" t="str">
-            <v>枫树</v>
+            <v>忘忧草</v>
           </cell>
           <cell r="C369">
-            <v>2500</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370">
-            <v>704020</v>
+            <v>704012</v>
           </cell>
           <cell r="B370" t="str">
-            <v>桦树</v>
+            <v>夏日浆果</v>
           </cell>
           <cell r="C370">
             <v>2500</v>
@@ -5131,318 +5207,318 @@
         </row>
         <row r="371">
           <cell r="A371">
-            <v>705001</v>
+            <v>704013</v>
           </cell>
           <cell r="B371" t="str">
-            <v>农夫雕像</v>
+            <v>秋日浆果</v>
           </cell>
           <cell r="C371">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372">
-            <v>705002</v>
+            <v>704014</v>
           </cell>
           <cell r="B372" t="str">
-            <v>精灵雕像</v>
+            <v>冬日浆果</v>
           </cell>
           <cell r="C372">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373">
-            <v>705003</v>
+            <v>704015</v>
           </cell>
           <cell r="B373" t="str">
-            <v>士兵雕像</v>
+            <v>樟树</v>
           </cell>
           <cell r="C373">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374">
-            <v>705004</v>
+            <v>704016</v>
           </cell>
           <cell r="B374" t="str">
-            <v>渔夫雕像</v>
+            <v>榕树</v>
           </cell>
           <cell r="C374">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375">
-            <v>705005</v>
+            <v>704017</v>
           </cell>
           <cell r="B375" t="str">
-            <v>牧民雕像</v>
+            <v>梧桐</v>
           </cell>
           <cell r="C375">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376">
-            <v>705006</v>
+            <v>704018</v>
           </cell>
           <cell r="B376" t="str">
-            <v>BUG雕像</v>
+            <v>松树</v>
           </cell>
           <cell r="C376">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377">
-            <v>706001</v>
+            <v>704019</v>
           </cell>
           <cell r="B377" t="str">
-            <v>货船</v>
+            <v>枫树</v>
           </cell>
           <cell r="C377">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="378">
           <cell r="A378">
-            <v>706002</v>
+            <v>704020</v>
           </cell>
           <cell r="B378" t="str">
-            <v>战舰</v>
+            <v>桦树</v>
           </cell>
           <cell r="C378">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="379">
           <cell r="A379">
-            <v>706003</v>
+            <v>704021</v>
           </cell>
           <cell r="B379" t="str">
-            <v>巨型战舰</v>
+            <v>荧光红蘑菇</v>
           </cell>
           <cell r="C379">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="380">
           <cell r="A380">
-            <v>707001</v>
+            <v>704022</v>
           </cell>
           <cell r="B380" t="str">
-            <v>甘蔗种子</v>
+            <v>荧光蓝蘑菇</v>
           </cell>
           <cell r="C380">
-            <v>10000</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="381">
           <cell r="A381">
-            <v>801001</v>
+            <v>704023</v>
           </cell>
           <cell r="B381" t="str">
-            <v>死亡的鸡</v>
+            <v>荧光绿蘑菇</v>
           </cell>
           <cell r="C381">
-            <v>0</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="382">
           <cell r="A382">
-            <v>801002</v>
+            <v>704024</v>
           </cell>
           <cell r="B382" t="str">
-            <v>死亡的羊</v>
+            <v>光亮蘑菇</v>
           </cell>
           <cell r="C382">
-            <v>0</v>
+            <v>2500</v>
           </cell>
         </row>
         <row r="383">
           <cell r="A383">
-            <v>801003</v>
+            <v>704025</v>
           </cell>
           <cell r="B383" t="str">
-            <v>死亡的牛</v>
+            <v>向日葵</v>
           </cell>
           <cell r="C383">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="384">
           <cell r="A384">
-            <v>801004</v>
+            <v>704026</v>
           </cell>
           <cell r="B384" t="str">
-            <v>死亡的马</v>
+            <v>白玫瑰</v>
           </cell>
           <cell r="C384">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="385">
           <cell r="A385">
-            <v>801005</v>
+            <v>704027</v>
           </cell>
           <cell r="B385" t="str">
-            <v>死亡的猪</v>
+            <v>红玫瑰</v>
           </cell>
           <cell r="C385">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="386">
           <cell r="A386">
-            <v>801006</v>
+            <v>704028</v>
           </cell>
           <cell r="B386" t="str">
-            <v>死亡的狼</v>
+            <v>蓝玫瑰</v>
           </cell>
           <cell r="C386">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="387">
           <cell r="A387">
-            <v>801007</v>
+            <v>704029</v>
           </cell>
           <cell r="B387" t="str">
-            <v>死亡的鹿</v>
+            <v>郁金香</v>
           </cell>
           <cell r="C387">
-            <v>0</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="388">
           <cell r="A388">
-            <v>801008</v>
+            <v>705001</v>
           </cell>
           <cell r="B388" t="str">
-            <v>死亡的白鹿</v>
+            <v>农夫雕像</v>
           </cell>
           <cell r="C388">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="389">
           <cell r="A389">
-            <v>801009</v>
+            <v>705002</v>
           </cell>
           <cell r="B389" t="str">
-            <v>死亡的梅花鹿</v>
+            <v>精灵雕像</v>
           </cell>
           <cell r="C389">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="390">
           <cell r="A390">
-            <v>802001</v>
+            <v>705003</v>
           </cell>
           <cell r="B390" t="str">
-            <v>种子商人贸易船</v>
+            <v>士兵雕像</v>
           </cell>
           <cell r="C390">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="391">
           <cell r="A391">
-            <v>802002</v>
+            <v>705004</v>
           </cell>
           <cell r="B391" t="str">
-            <v>食品商人贸易船</v>
+            <v>渔夫雕像</v>
           </cell>
           <cell r="C391">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="392">
           <cell r="A392">
-            <v>802003</v>
+            <v>705005</v>
           </cell>
           <cell r="B392" t="str">
-            <v>杂货商人贸易船</v>
+            <v>牧民雕像</v>
           </cell>
           <cell r="C392">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="393">
           <cell r="A393">
-            <v>802004</v>
+            <v>705006</v>
           </cell>
           <cell r="B393" t="str">
-            <v>牲畜商人贸易船</v>
+            <v>BUG雕像</v>
           </cell>
           <cell r="C393">
-            <v>0</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="394">
           <cell r="A394">
-            <v>802005</v>
+            <v>705007</v>
           </cell>
           <cell r="B394" t="str">
-            <v>代购商人贸易船</v>
+            <v>鲜花雕像</v>
           </cell>
           <cell r="C394">
-            <v>0</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="395">
           <cell r="A395">
-            <v>803001</v>
+            <v>706001</v>
           </cell>
           <cell r="B395" t="str">
-            <v>水</v>
+            <v>货船</v>
           </cell>
           <cell r="C395">
-            <v>0</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="396">
           <cell r="A396">
-            <v>804001</v>
+            <v>706002</v>
           </cell>
           <cell r="B396" t="str">
-            <v>尸体</v>
+            <v>战舰</v>
           </cell>
           <cell r="C396">
-            <v>0</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="397">
           <cell r="A397">
-            <v>805001</v>
+            <v>706003</v>
           </cell>
           <cell r="B397" t="str">
-            <v>大鱼</v>
+            <v>巨型战舰</v>
           </cell>
           <cell r="C397">
-            <v>0</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="398">
           <cell r="A398">
-            <v>806001</v>
+            <v>707001</v>
           </cell>
           <cell r="B398" t="str">
-            <v>种子商人</v>
+            <v>甘蔗种子</v>
           </cell>
           <cell r="C398">
-            <v>0</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="399">
           <cell r="A399">
-            <v>806002</v>
+            <v>801001</v>
           </cell>
           <cell r="B399" t="str">
-            <v>食品商人</v>
+            <v>死亡的鸡</v>
           </cell>
           <cell r="C399">
             <v>0</v>
@@ -5450,10 +5526,10 @@
         </row>
         <row r="400">
           <cell r="A400">
-            <v>806003</v>
+            <v>801002</v>
           </cell>
           <cell r="B400" t="str">
-            <v>杂货商人</v>
+            <v>死亡的羊</v>
           </cell>
           <cell r="C400">
             <v>0</v>
@@ -5461,10 +5537,10 @@
         </row>
         <row r="401">
           <cell r="A401">
-            <v>806004</v>
+            <v>801003</v>
           </cell>
           <cell r="B401" t="str">
-            <v>牲畜商人</v>
+            <v>死亡的牛</v>
           </cell>
           <cell r="C401">
             <v>0</v>
@@ -5472,10 +5548,10 @@
         </row>
         <row r="402">
           <cell r="A402">
-            <v>806005</v>
+            <v>801004</v>
           </cell>
           <cell r="B402" t="str">
-            <v>两轮马车</v>
+            <v>死亡的马</v>
           </cell>
           <cell r="C402">
             <v>0</v>
@@ -5483,10 +5559,10 @@
         </row>
         <row r="403">
           <cell r="A403">
-            <v>806006</v>
+            <v>801005</v>
           </cell>
           <cell r="B403" t="str">
-            <v>四轮马车</v>
+            <v>死亡的猪</v>
           </cell>
           <cell r="C403">
             <v>0</v>
@@ -5494,43 +5570,43 @@
         </row>
         <row r="404">
           <cell r="A404">
-            <v>807001</v>
+            <v>801006</v>
           </cell>
           <cell r="B404" t="str">
-            <v>马战车</v>
+            <v>死亡的狼</v>
           </cell>
           <cell r="C404">
-            <v>5000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="405">
           <cell r="A405">
-            <v>807002</v>
+            <v>801007</v>
           </cell>
           <cell r="B405" t="str">
-            <v>狼战车</v>
+            <v>死亡的鹿</v>
           </cell>
           <cell r="C405">
-            <v>5000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="406">
           <cell r="A406">
-            <v>807003</v>
+            <v>801008</v>
           </cell>
           <cell r="B406" t="str">
-            <v>猪战车</v>
+            <v>死亡的白鹿</v>
           </cell>
           <cell r="C406">
-            <v>5000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="407">
           <cell r="A407">
-            <v>808001</v>
+            <v>801009</v>
           </cell>
           <cell r="B407" t="str">
-            <v>???</v>
+            <v>死亡的梅花鹿</v>
           </cell>
           <cell r="C407">
             <v>0</v>
@@ -5538,10 +5614,10 @@
         </row>
         <row r="408">
           <cell r="A408">
-            <v>809001</v>
+            <v>802001</v>
           </cell>
           <cell r="B408" t="str">
-            <v>鼻涕</v>
+            <v>种子商人贸易船</v>
           </cell>
           <cell r="C408">
             <v>0</v>
@@ -5549,10 +5625,10 @@
         </row>
         <row r="409">
           <cell r="A409">
-            <v>810001</v>
+            <v>802002</v>
           </cell>
           <cell r="B409" t="str">
-            <v>宝藏标记</v>
+            <v>食品商人贸易船</v>
           </cell>
           <cell r="C409">
             <v>0</v>
@@ -5560,10 +5636,10 @@
         </row>
         <row r="410">
           <cell r="A410">
-            <v>810002</v>
+            <v>802003</v>
           </cell>
           <cell r="B410" t="str">
-            <v>宝箱</v>
+            <v>杂货商人贸易船</v>
           </cell>
           <cell r="C410">
             <v>0</v>
@@ -5571,10 +5647,10 @@
         </row>
         <row r="411">
           <cell r="A411">
-            <v>811001</v>
+            <v>802004</v>
           </cell>
           <cell r="B411" t="str">
-            <v>生命之力</v>
+            <v>牲畜商人贸易船</v>
           </cell>
           <cell r="C411">
             <v>0</v>
@@ -5582,10 +5658,10 @@
         </row>
         <row r="412">
           <cell r="A412">
-            <v>812000</v>
+            <v>802005</v>
           </cell>
           <cell r="B412" t="str">
-            <v>矮人</v>
+            <v>代购商人贸易船</v>
           </cell>
           <cell r="C412">
             <v>0</v>
@@ -5593,10 +5669,10 @@
         </row>
         <row r="413">
           <cell r="A413">
-            <v>812001</v>
+            <v>803001</v>
           </cell>
           <cell r="B413" t="str">
-            <v>蚁人</v>
+            <v>水</v>
           </cell>
           <cell r="C413">
             <v>0</v>
@@ -5604,10 +5680,10 @@
         </row>
         <row r="414">
           <cell r="A414">
-            <v>812002</v>
+            <v>804001</v>
           </cell>
           <cell r="B414" t="str">
-            <v>鼠人</v>
+            <v>尸体</v>
           </cell>
           <cell r="C414">
             <v>0</v>
@@ -5615,10 +5691,10 @@
         </row>
         <row r="415">
           <cell r="A415">
-            <v>812003</v>
+            <v>805001</v>
           </cell>
           <cell r="B415" t="str">
-            <v>猫人</v>
+            <v>大鱼</v>
           </cell>
           <cell r="C415">
             <v>0</v>
@@ -5626,10 +5702,10 @@
         </row>
         <row r="416">
           <cell r="A416">
-            <v>812004</v>
+            <v>806001</v>
           </cell>
           <cell r="B416" t="str">
-            <v>羊人</v>
+            <v>种子商人</v>
           </cell>
           <cell r="C416">
             <v>0</v>
@@ -5637,10 +5713,10 @@
         </row>
         <row r="417">
           <cell r="A417">
-            <v>812005</v>
+            <v>806002</v>
           </cell>
           <cell r="B417" t="str">
-            <v>狼人</v>
+            <v>食品商人</v>
           </cell>
           <cell r="C417">
             <v>0</v>
@@ -5648,10 +5724,10 @@
         </row>
         <row r="418">
           <cell r="A418">
-            <v>812006</v>
+            <v>806003</v>
           </cell>
           <cell r="B418" t="str">
-            <v>猪人</v>
+            <v>杂货商人</v>
           </cell>
           <cell r="C418">
             <v>0</v>
@@ -5659,10 +5735,10 @@
         </row>
         <row r="419">
           <cell r="A419">
-            <v>812007</v>
+            <v>806004</v>
           </cell>
           <cell r="B419" t="str">
-            <v>精灵族</v>
+            <v>牲畜商人</v>
           </cell>
           <cell r="C419">
             <v>0</v>
@@ -5670,10 +5746,10 @@
         </row>
         <row r="420">
           <cell r="A420">
-            <v>812008</v>
+            <v>806005</v>
           </cell>
           <cell r="B420" t="str">
-            <v>三眼人</v>
+            <v>两轮马车</v>
           </cell>
           <cell r="C420">
             <v>0</v>
@@ -5681,10 +5757,10 @@
         </row>
         <row r="421">
           <cell r="A421">
-            <v>812009</v>
+            <v>806006</v>
           </cell>
           <cell r="B421" t="str">
-            <v>蜥蜴人</v>
+            <v>四轮马车</v>
           </cell>
           <cell r="C421">
             <v>0</v>
@@ -5692,43 +5768,43 @@
         </row>
         <row r="422">
           <cell r="A422">
-            <v>813001</v>
+            <v>807001</v>
           </cell>
           <cell r="B422" t="str">
-            <v>蜜糖派对</v>
+            <v>马战车</v>
           </cell>
           <cell r="C422">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="423">
           <cell r="A423">
-            <v>813002</v>
+            <v>807002</v>
           </cell>
           <cell r="B423" t="str">
-            <v>药茶品鉴会</v>
+            <v>狼战车</v>
           </cell>
           <cell r="C423">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="424">
           <cell r="A424">
-            <v>813003</v>
+            <v>807003</v>
           </cell>
           <cell r="B424" t="str">
-            <v>水果蔬菜沙龙</v>
+            <v>猪战车</v>
           </cell>
           <cell r="C424">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="425">
           <cell r="A425">
-            <v>813004</v>
+            <v>808001</v>
           </cell>
           <cell r="B425" t="str">
-            <v>酒神狂欢节</v>
+            <v>???</v>
           </cell>
           <cell r="C425">
             <v>0</v>
@@ -5736,10 +5812,10 @@
         </row>
         <row r="426">
           <cell r="A426">
-            <v>813005</v>
+            <v>809001</v>
           </cell>
           <cell r="B426" t="str">
-            <v>黑暗料理派对</v>
+            <v>鼻涕</v>
           </cell>
           <cell r="C426">
             <v>0</v>
@@ -5747,10 +5823,10 @@
         </row>
         <row r="427">
           <cell r="A427">
-            <v>813006</v>
+            <v>810001</v>
           </cell>
           <cell r="B427" t="str">
-            <v>鱼肉生鲜派对</v>
+            <v>宝藏标记</v>
           </cell>
           <cell r="C427">
             <v>0</v>
@@ -5758,10 +5834,10 @@
         </row>
         <row r="428">
           <cell r="A428">
-            <v>813007</v>
+            <v>810002</v>
           </cell>
           <cell r="B428" t="str">
-            <v>宝石品鉴会</v>
+            <v>宝箱</v>
           </cell>
           <cell r="C428">
             <v>0</v>
@@ -5769,10 +5845,10 @@
         </row>
         <row r="429">
           <cell r="A429">
-            <v>813008</v>
+            <v>811001</v>
           </cell>
           <cell r="B429" t="str">
-            <v>文化研讨会</v>
+            <v>生命之力</v>
           </cell>
           <cell r="C429">
             <v>0</v>
@@ -5780,10 +5856,10 @@
         </row>
         <row r="430">
           <cell r="A430">
-            <v>813009</v>
+            <v>812000</v>
           </cell>
           <cell r="B430" t="str">
-            <v>贵族派对</v>
+            <v>矮人</v>
           </cell>
           <cell r="C430">
             <v>0</v>
@@ -5791,10 +5867,10 @@
         </row>
         <row r="431">
           <cell r="A431">
-            <v>814001</v>
+            <v>812001</v>
           </cell>
           <cell r="B431" t="str">
-            <v>青青草原</v>
+            <v>蚁人</v>
           </cell>
           <cell r="C431">
             <v>0</v>
@@ -5802,10 +5878,10 @@
         </row>
         <row r="432">
           <cell r="A432">
-            <v>814002</v>
+            <v>812002</v>
           </cell>
           <cell r="B432" t="str">
-            <v>北部森林</v>
+            <v>鼠人</v>
           </cell>
           <cell r="C432">
             <v>0</v>
@@ -5813,10 +5889,10 @@
         </row>
         <row r="433">
           <cell r="A433">
-            <v>814003</v>
+            <v>812003</v>
           </cell>
           <cell r="B433" t="str">
-            <v>无人荒野</v>
+            <v>猫人</v>
           </cell>
           <cell r="C433">
             <v>0</v>
@@ -5824,10 +5900,10 @@
         </row>
         <row r="434">
           <cell r="A434">
-            <v>814004</v>
+            <v>812004</v>
           </cell>
           <cell r="B434" t="str">
-            <v>黄昏森林</v>
+            <v>羊人</v>
           </cell>
           <cell r="C434">
             <v>0</v>
@@ -5835,10 +5911,10 @@
         </row>
         <row r="435">
           <cell r="A435">
-            <v>814005</v>
+            <v>812005</v>
           </cell>
           <cell r="B435" t="str">
-            <v>野蛮荒野</v>
+            <v>狼人</v>
           </cell>
           <cell r="C435">
             <v>0</v>
@@ -5846,10 +5922,10 @@
         </row>
         <row r="436">
           <cell r="A436">
-            <v>814006</v>
+            <v>812006</v>
           </cell>
           <cell r="B436" t="str">
-            <v>迷雾山峰</v>
+            <v>猪人</v>
           </cell>
           <cell r="C436">
             <v>0</v>
@@ -5857,10 +5933,10 @@
         </row>
         <row r="437">
           <cell r="A437">
-            <v>814007</v>
+            <v>812007</v>
           </cell>
           <cell r="B437" t="str">
-            <v>滨海平原</v>
+            <v>精灵族</v>
           </cell>
           <cell r="C437">
             <v>0</v>
@@ -5868,10 +5944,10 @@
         </row>
         <row r="438">
           <cell r="A438">
-            <v>814008</v>
+            <v>812008</v>
           </cell>
           <cell r="B438" t="str">
-            <v>恶魔海角</v>
+            <v>三眼人</v>
           </cell>
           <cell r="C438">
             <v>0</v>
@@ -5879,10 +5955,10 @@
         </row>
         <row r="439">
           <cell r="A439">
-            <v>814009</v>
+            <v>812009</v>
           </cell>
           <cell r="B439" t="str">
-            <v>龙之平原</v>
+            <v>蜥蜴人</v>
           </cell>
           <cell r="C439">
             <v>0</v>
@@ -5890,10 +5966,10 @@
         </row>
         <row r="440">
           <cell r="A440">
-            <v>814010</v>
+            <v>813001</v>
           </cell>
           <cell r="B440" t="str">
-            <v>龙之峡谷</v>
+            <v>蜜糖派对</v>
           </cell>
           <cell r="C440">
             <v>0</v>
@@ -5901,65 +5977,65 @@
         </row>
         <row r="441">
           <cell r="A441">
-            <v>815001</v>
+            <v>813002</v>
           </cell>
           <cell r="B441" t="str">
-            <v>龙魂石</v>
+            <v>药茶品鉴会</v>
           </cell>
           <cell r="C441">
-            <v>20000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="442">
           <cell r="A442">
-            <v>815002</v>
+            <v>813003</v>
           </cell>
           <cell r="B442" t="str">
-            <v>龙鳞</v>
+            <v>水果蔬菜沙龙</v>
           </cell>
           <cell r="C442">
-            <v>20000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="443">
           <cell r="A443">
-            <v>815003</v>
+            <v>813004</v>
           </cell>
           <cell r="B443" t="str">
-            <v>龙晶</v>
+            <v>酒神狂欢节</v>
           </cell>
           <cell r="C443">
-            <v>20000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="444">
           <cell r="A444">
-            <v>815004</v>
+            <v>813005</v>
           </cell>
           <cell r="B444" t="str">
-            <v>龙髓</v>
+            <v>黑暗料理派对</v>
           </cell>
           <cell r="C444">
-            <v>20000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="445">
           <cell r="A445">
-            <v>815005</v>
+            <v>813006</v>
           </cell>
           <cell r="B445" t="str">
-            <v>龙蕊</v>
+            <v>鱼肉生鲜派对</v>
           </cell>
           <cell r="C445">
-            <v>20000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="446">
           <cell r="A446">
-            <v>901001</v>
+            <v>813007</v>
           </cell>
           <cell r="B446" t="str">
-            <v>一神教</v>
+            <v>宝石品鉴会</v>
           </cell>
           <cell r="C446">
             <v>0</v>
@@ -5967,10 +6043,10 @@
         </row>
         <row r="447">
           <cell r="A447">
-            <v>901002</v>
+            <v>813008</v>
           </cell>
           <cell r="B447" t="str">
-            <v>仁义道</v>
+            <v>文化研讨会</v>
           </cell>
           <cell r="C447">
             <v>0</v>
@@ -5978,10 +6054,10 @@
         </row>
         <row r="448">
           <cell r="A448">
-            <v>901004</v>
+            <v>813009</v>
           </cell>
           <cell r="B448" t="str">
-            <v>萨满教</v>
+            <v>贵族派对</v>
           </cell>
           <cell r="C448">
             <v>0</v>
@@ -5989,230 +6065,230 @@
         </row>
         <row r="449">
           <cell r="A449">
-            <v>902002</v>
+            <v>814001</v>
           </cell>
           <cell r="B449" t="str">
-            <v>登山技术</v>
+            <v>青青草原</v>
           </cell>
           <cell r="C449">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="450">
           <cell r="A450">
-            <v>902003</v>
+            <v>814002</v>
           </cell>
           <cell r="B450" t="str">
-            <v>石匠技术</v>
+            <v>北部森林</v>
           </cell>
           <cell r="C450">
-            <v>500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="451">
           <cell r="A451">
-            <v>902004</v>
+            <v>814003</v>
           </cell>
           <cell r="B451" t="str">
-            <v>周转箱</v>
+            <v>无人荒野</v>
           </cell>
           <cell r="C451">
-            <v>1000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="452">
           <cell r="A452">
-            <v>902005</v>
+            <v>814004</v>
           </cell>
           <cell r="B452" t="str">
-            <v>贸易</v>
+            <v>黄昏森林</v>
           </cell>
           <cell r="C452">
-            <v>1000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="453">
           <cell r="A453">
-            <v>902007</v>
+            <v>814005</v>
           </cell>
           <cell r="B453" t="str">
-            <v>酿酒</v>
+            <v>野蛮荒野</v>
           </cell>
           <cell r="C453">
-            <v>500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="454">
           <cell r="A454">
-            <v>902008</v>
+            <v>814006</v>
           </cell>
           <cell r="B454" t="str">
-            <v>教育</v>
+            <v>迷雾山峰</v>
           </cell>
           <cell r="C454">
-            <v>1000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="455">
           <cell r="A455">
-            <v>902009</v>
+            <v>814007</v>
           </cell>
           <cell r="B455" t="str">
-            <v>文化信仰</v>
+            <v>滨海平原</v>
           </cell>
           <cell r="C455">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="456">
           <cell r="A456">
-            <v>902010</v>
+            <v>814008</v>
           </cell>
           <cell r="B456" t="str">
-            <v>医疗</v>
+            <v>恶魔海角</v>
           </cell>
           <cell r="C456">
-            <v>1500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="457">
           <cell r="A457">
-            <v>902011</v>
+            <v>814009</v>
           </cell>
           <cell r="B457" t="str">
-            <v>制药</v>
+            <v>龙之平原</v>
           </cell>
           <cell r="C457">
-            <v>1500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="458">
           <cell r="A458">
-            <v>902012</v>
+            <v>814010</v>
           </cell>
           <cell r="B458" t="str">
-            <v>轮伐护林</v>
+            <v>龙之峡谷</v>
           </cell>
           <cell r="C458">
-            <v>500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="459">
           <cell r="A459">
-            <v>902013</v>
+            <v>815001</v>
           </cell>
           <cell r="B459" t="str">
-            <v>手工制造</v>
+            <v>龙魂石</v>
           </cell>
           <cell r="C459">
-            <v>500</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="460">
           <cell r="A460">
-            <v>902014</v>
+            <v>815002</v>
           </cell>
           <cell r="B460" t="str">
-            <v>地下采矿</v>
+            <v>龙鳞</v>
           </cell>
           <cell r="C460">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="461">
           <cell r="A461">
-            <v>902015</v>
+            <v>815003</v>
           </cell>
           <cell r="B461" t="str">
-            <v>地下采石</v>
+            <v>龙晶</v>
           </cell>
           <cell r="C461">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="462">
           <cell r="A462">
-            <v>902016</v>
+            <v>815004</v>
           </cell>
           <cell r="B462" t="str">
-            <v>福利事业</v>
+            <v>龙髓</v>
           </cell>
           <cell r="C462">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="463">
           <cell r="A463">
-            <v>902017</v>
+            <v>815005</v>
           </cell>
           <cell r="B463" t="str">
-            <v>水井</v>
+            <v>龙蕊</v>
           </cell>
           <cell r="C463">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="464">
           <cell r="A464">
-            <v>902018</v>
+            <v>816001</v>
           </cell>
           <cell r="B464" t="str">
-            <v>施肥增产</v>
+            <v>高级郁金香</v>
           </cell>
           <cell r="C464">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="465">
           <cell r="A465">
-            <v>902019</v>
+            <v>816002</v>
           </cell>
           <cell r="B465" t="str">
-            <v>成片播种</v>
+            <v>稀有郁金香</v>
           </cell>
           <cell r="C465">
-            <v>2000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="466">
           <cell r="A466">
-            <v>902020</v>
+            <v>901001</v>
           </cell>
           <cell r="B466" t="str">
-            <v>成片浇水</v>
+            <v>一神教</v>
           </cell>
           <cell r="C466">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="467">
           <cell r="A467">
-            <v>902021</v>
+            <v>901002</v>
           </cell>
           <cell r="B467" t="str">
-            <v>成片收割</v>
+            <v>仁义道</v>
           </cell>
           <cell r="C467">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="468">
           <cell r="A468">
-            <v>902022</v>
+            <v>901004</v>
           </cell>
           <cell r="B468" t="str">
-            <v>采集</v>
+            <v>萨满教</v>
           </cell>
           <cell r="C468">
-            <v>2000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="469">
           <cell r="A469">
-            <v>902023</v>
+            <v>902002</v>
           </cell>
           <cell r="B469" t="str">
-            <v>捕兽夹</v>
+            <v>登山技术</v>
           </cell>
           <cell r="C469">
             <v>2000</v>
@@ -6220,65 +6296,65 @@
         </row>
         <row r="470">
           <cell r="A470">
-            <v>902024</v>
+            <v>902003</v>
           </cell>
           <cell r="B470" t="str">
-            <v>蟹笼</v>
+            <v>石匠技术</v>
           </cell>
           <cell r="C470">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="471">
           <cell r="A471">
-            <v>902025</v>
+            <v>902004</v>
           </cell>
           <cell r="B471" t="str">
-            <v>军事</v>
+            <v>周转箱</v>
           </cell>
           <cell r="C471">
-            <v>2000</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="472">
           <cell r="A472">
-            <v>902032</v>
+            <v>902005</v>
           </cell>
           <cell r="B472" t="str">
-            <v>一神教思想</v>
+            <v>贸易</v>
           </cell>
           <cell r="C472">
-            <v>2000</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="473">
           <cell r="A473">
-            <v>902033</v>
+            <v>902007</v>
           </cell>
           <cell r="B473" t="str">
-            <v>仁义道思想</v>
+            <v>酿酒</v>
           </cell>
           <cell r="C473">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="474">
           <cell r="A474">
-            <v>902034</v>
+            <v>902008</v>
           </cell>
           <cell r="B474" t="str">
-            <v>狩猎</v>
+            <v>教育</v>
           </cell>
           <cell r="C474">
-            <v>2000</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="475">
           <cell r="A475">
-            <v>902035</v>
+            <v>902009</v>
           </cell>
           <cell r="B475" t="str">
-            <v>捕鱼</v>
+            <v>文化信仰</v>
           </cell>
           <cell r="C475">
             <v>2000</v>
@@ -6286,54 +6362,54 @@
         </row>
         <row r="476">
           <cell r="A476">
-            <v>902036</v>
+            <v>902010</v>
           </cell>
           <cell r="B476" t="str">
-            <v>种植</v>
+            <v>医疗</v>
           </cell>
           <cell r="C476">
-            <v>2000</v>
+            <v>1500</v>
           </cell>
         </row>
         <row r="477">
           <cell r="A477">
-            <v>902037</v>
+            <v>902011</v>
           </cell>
           <cell r="B477" t="str">
-            <v>养殖</v>
+            <v>制药</v>
           </cell>
           <cell r="C477">
-            <v>2000</v>
+            <v>1500</v>
           </cell>
         </row>
         <row r="478">
           <cell r="A478">
-            <v>902038</v>
+            <v>902012</v>
           </cell>
           <cell r="B478" t="str">
-            <v>养蜂</v>
+            <v>轮伐护林</v>
           </cell>
           <cell r="C478">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="479">
           <cell r="A479">
-            <v>902039</v>
+            <v>902013</v>
           </cell>
           <cell r="B479" t="str">
-            <v>盆栽</v>
+            <v>手工制造</v>
           </cell>
           <cell r="C479">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="480">
           <cell r="A480">
-            <v>902049</v>
+            <v>902014</v>
           </cell>
           <cell r="B480" t="str">
-            <v>普通武器</v>
+            <v>地下采矿</v>
           </cell>
           <cell r="C480">
             <v>2000</v>
@@ -6341,10 +6417,10 @@
         </row>
         <row r="481">
           <cell r="A481">
-            <v>902026</v>
+            <v>902015</v>
           </cell>
           <cell r="B481" t="str">
-            <v>优良武器</v>
+            <v>地下采石</v>
           </cell>
           <cell r="C481">
             <v>2000</v>
@@ -6352,10 +6428,10 @@
         </row>
         <row r="482">
           <cell r="A482">
-            <v>902029</v>
+            <v>902016</v>
           </cell>
           <cell r="B482" t="str">
-            <v>高级武器</v>
+            <v>福利事业</v>
           </cell>
           <cell r="C482">
             <v>2000</v>
@@ -6363,10 +6439,10 @@
         </row>
         <row r="483">
           <cell r="A483">
-            <v>902040</v>
+            <v>902017</v>
           </cell>
           <cell r="B483" t="str">
-            <v>稀有武器</v>
+            <v>水井</v>
           </cell>
           <cell r="C483">
             <v>2000</v>
@@ -6374,10 +6450,10 @@
         </row>
         <row r="484">
           <cell r="A484">
-            <v>902043</v>
+            <v>902018</v>
           </cell>
           <cell r="B484" t="str">
-            <v>特殊武器</v>
+            <v>施肥增产</v>
           </cell>
           <cell r="C484">
             <v>2000</v>
@@ -6385,10 +6461,10 @@
         </row>
         <row r="485">
           <cell r="A485">
-            <v>902046</v>
+            <v>902019</v>
           </cell>
           <cell r="B485" t="str">
-            <v>极品武器</v>
+            <v>成片播种</v>
           </cell>
           <cell r="C485">
             <v>2000</v>
@@ -6396,10 +6472,10 @@
         </row>
         <row r="486">
           <cell r="A486">
-            <v>902068</v>
+            <v>902020</v>
           </cell>
           <cell r="B486" t="str">
-            <v>传说武器</v>
+            <v>成片浇水</v>
           </cell>
           <cell r="C486">
             <v>2000</v>
@@ -6407,10 +6483,10 @@
         </row>
         <row r="487">
           <cell r="A487">
-            <v>902071</v>
+            <v>902021</v>
           </cell>
           <cell r="B487" t="str">
-            <v>史诗武器</v>
+            <v>成片收割</v>
           </cell>
           <cell r="C487">
             <v>2000</v>
@@ -6418,10 +6494,10 @@
         </row>
         <row r="488">
           <cell r="A488">
-            <v>902050</v>
+            <v>902022</v>
           </cell>
           <cell r="B488" t="str">
-            <v>普通盔甲</v>
+            <v>采集</v>
           </cell>
           <cell r="C488">
             <v>2000</v>
@@ -6429,10 +6505,10 @@
         </row>
         <row r="489">
           <cell r="A489">
-            <v>902027</v>
+            <v>902023</v>
           </cell>
           <cell r="B489" t="str">
-            <v>优良盔甲</v>
+            <v>捕兽夹</v>
           </cell>
           <cell r="C489">
             <v>2000</v>
@@ -6440,10 +6516,10 @@
         </row>
         <row r="490">
           <cell r="A490">
-            <v>902030</v>
+            <v>902024</v>
           </cell>
           <cell r="B490" t="str">
-            <v>高级盔甲</v>
+            <v>蟹笼</v>
           </cell>
           <cell r="C490">
             <v>2000</v>
@@ -6451,10 +6527,10 @@
         </row>
         <row r="491">
           <cell r="A491">
-            <v>902041</v>
+            <v>902025</v>
           </cell>
           <cell r="B491" t="str">
-            <v>稀有盔甲</v>
+            <v>军事</v>
           </cell>
           <cell r="C491">
             <v>2000</v>
@@ -6462,10 +6538,10 @@
         </row>
         <row r="492">
           <cell r="A492">
-            <v>902044</v>
+            <v>902032</v>
           </cell>
           <cell r="B492" t="str">
-            <v>特殊盔甲</v>
+            <v>一神教思想</v>
           </cell>
           <cell r="C492">
             <v>2000</v>
@@ -6473,10 +6549,10 @@
         </row>
         <row r="493">
           <cell r="A493">
-            <v>902047</v>
+            <v>902033</v>
           </cell>
           <cell r="B493" t="str">
-            <v>极品盔甲</v>
+            <v>仁义道思想</v>
           </cell>
           <cell r="C493">
             <v>2000</v>
@@ -6484,10 +6560,10 @@
         </row>
         <row r="494">
           <cell r="A494">
-            <v>902069</v>
+            <v>902034</v>
           </cell>
           <cell r="B494" t="str">
-            <v>传说盔甲</v>
+            <v>狩猎</v>
           </cell>
           <cell r="C494">
             <v>2000</v>
@@ -6495,10 +6571,10 @@
         </row>
         <row r="495">
           <cell r="A495">
-            <v>902072</v>
+            <v>902035</v>
           </cell>
           <cell r="B495" t="str">
-            <v>史诗盔甲</v>
+            <v>捕鱼</v>
           </cell>
           <cell r="C495">
             <v>2000</v>
@@ -6506,10 +6582,10 @@
         </row>
         <row r="496">
           <cell r="A496">
-            <v>902051</v>
+            <v>902036</v>
           </cell>
           <cell r="B496" t="str">
-            <v>普通盾牌</v>
+            <v>农田</v>
           </cell>
           <cell r="C496">
             <v>2000</v>
@@ -6517,10 +6593,10 @@
         </row>
         <row r="497">
           <cell r="A497">
-            <v>902028</v>
+            <v>902037</v>
           </cell>
           <cell r="B497" t="str">
-            <v>优良盾牌</v>
+            <v>养殖</v>
           </cell>
           <cell r="C497">
             <v>2000</v>
@@ -6528,10 +6604,10 @@
         </row>
         <row r="498">
           <cell r="A498">
-            <v>902031</v>
+            <v>902038</v>
           </cell>
           <cell r="B498" t="str">
-            <v>高级盾牌</v>
+            <v>养蜂</v>
           </cell>
           <cell r="C498">
             <v>2000</v>
@@ -6539,10 +6615,10 @@
         </row>
         <row r="499">
           <cell r="A499">
-            <v>902042</v>
+            <v>902039</v>
           </cell>
           <cell r="B499" t="str">
-            <v>稀有盾牌</v>
+            <v>盆栽</v>
           </cell>
           <cell r="C499">
             <v>2000</v>
@@ -6550,10 +6626,10 @@
         </row>
         <row r="500">
           <cell r="A500">
-            <v>902045</v>
+            <v>902049</v>
           </cell>
           <cell r="B500" t="str">
-            <v>特殊盾牌</v>
+            <v>普通武器</v>
           </cell>
           <cell r="C500">
             <v>2000</v>
@@ -6561,10 +6637,10 @@
         </row>
         <row r="501">
           <cell r="A501">
-            <v>902048</v>
+            <v>902026</v>
           </cell>
           <cell r="B501" t="str">
-            <v>极品盾牌</v>
+            <v>优良武器</v>
           </cell>
           <cell r="C501">
             <v>2000</v>
@@ -6572,10 +6648,10 @@
         </row>
         <row r="502">
           <cell r="A502">
-            <v>902070</v>
+            <v>902029</v>
           </cell>
           <cell r="B502" t="str">
-            <v>传说盾牌</v>
+            <v>高级武器</v>
           </cell>
           <cell r="C502">
             <v>2000</v>
@@ -6583,10 +6659,10 @@
         </row>
         <row r="503">
           <cell r="A503">
-            <v>902073</v>
+            <v>902040</v>
           </cell>
           <cell r="B503" t="str">
-            <v>史诗盾牌</v>
+            <v>稀有武器</v>
           </cell>
           <cell r="C503">
             <v>2000</v>
@@ -6594,10 +6670,10 @@
         </row>
         <row r="504">
           <cell r="A504">
-            <v>902052</v>
+            <v>902043</v>
           </cell>
           <cell r="B504" t="str">
-            <v>锻造</v>
+            <v>特殊武器</v>
           </cell>
           <cell r="C504">
             <v>2000</v>
@@ -6605,10 +6681,10 @@
         </row>
         <row r="505">
           <cell r="A505">
-            <v>902053</v>
+            <v>902046</v>
           </cell>
           <cell r="B505" t="str">
-            <v>弓矢</v>
+            <v>极品武器</v>
           </cell>
           <cell r="C505">
             <v>2000</v>
@@ -6616,10 +6692,10 @@
         </row>
         <row r="506">
           <cell r="A506">
-            <v>902054</v>
+            <v>902068</v>
           </cell>
           <cell r="B506" t="str">
-            <v>弩机</v>
+            <v>传说武器</v>
           </cell>
           <cell r="C506">
             <v>2000</v>
@@ -6627,10 +6703,10 @@
         </row>
         <row r="507">
           <cell r="A507">
-            <v>902055</v>
+            <v>902071</v>
           </cell>
           <cell r="B507" t="str">
-            <v>盾牌</v>
+            <v>史诗武器</v>
           </cell>
           <cell r="C507">
             <v>2000</v>
@@ -6638,10 +6714,10 @@
         </row>
         <row r="508">
           <cell r="A508">
-            <v>902056</v>
+            <v>902050</v>
           </cell>
           <cell r="B508" t="str">
-            <v>巨盾</v>
+            <v>普通盔甲</v>
           </cell>
           <cell r="C508">
             <v>2000</v>
@@ -6649,10 +6725,10 @@
         </row>
         <row r="509">
           <cell r="A509">
-            <v>902057</v>
+            <v>902027</v>
           </cell>
           <cell r="B509" t="str">
-            <v>骑射</v>
+            <v>优良盔甲</v>
           </cell>
           <cell r="C509">
             <v>2000</v>
@@ -6660,10 +6736,10 @@
         </row>
         <row r="510">
           <cell r="A510">
-            <v>902059</v>
+            <v>902030</v>
           </cell>
           <cell r="B510" t="str">
-            <v>人伦书</v>
+            <v>高级盔甲</v>
           </cell>
           <cell r="C510">
             <v>2000</v>
@@ -6671,10 +6747,10 @@
         </row>
         <row r="511">
           <cell r="A511">
-            <v>902060</v>
+            <v>902041</v>
           </cell>
           <cell r="B511" t="str">
-            <v>轮回书</v>
+            <v>稀有盔甲</v>
           </cell>
           <cell r="C511">
             <v>2000</v>
@@ -6682,65 +6758,65 @@
         </row>
         <row r="512">
           <cell r="A512">
-            <v>902061</v>
+            <v>902044</v>
           </cell>
           <cell r="B512" t="str">
-            <v>货架</v>
+            <v>特殊盔甲</v>
           </cell>
           <cell r="C512">
-            <v>1000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="513">
           <cell r="A513">
-            <v>902063</v>
+            <v>902047</v>
           </cell>
           <cell r="B513" t="str">
-            <v>填水造陆</v>
+            <v>极品盔甲</v>
           </cell>
           <cell r="C513">
-            <v>1000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="514">
           <cell r="A514">
-            <v>902064</v>
+            <v>902069</v>
           </cell>
           <cell r="B514" t="str">
-            <v>开挖河道</v>
+            <v>传说盔甲</v>
           </cell>
           <cell r="C514">
-            <v>1000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="515">
           <cell r="A515">
-            <v>902065</v>
+            <v>902072</v>
           </cell>
           <cell r="B515" t="str">
-            <v>边境贸易</v>
+            <v>史诗盔甲</v>
           </cell>
           <cell r="C515">
-            <v>1000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="516">
           <cell r="A516">
-            <v>902066</v>
+            <v>902051</v>
           </cell>
           <cell r="B516" t="str">
-            <v>马车运输</v>
+            <v>普通盾牌</v>
           </cell>
           <cell r="C516">
-            <v>1000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="517">
           <cell r="A517">
-            <v>902074</v>
+            <v>902028</v>
           </cell>
           <cell r="B517" t="str">
-            <v>牢房</v>
+            <v>优良盾牌</v>
           </cell>
           <cell r="C517">
             <v>2000</v>
@@ -6748,230 +6824,230 @@
         </row>
         <row r="518">
           <cell r="A518">
-            <v>902075</v>
+            <v>902031</v>
           </cell>
           <cell r="B518" t="str">
-            <v>壁炉</v>
+            <v>高级盾牌</v>
           </cell>
           <cell r="C518">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="519">
           <cell r="A519">
-            <v>902077</v>
+            <v>902042</v>
           </cell>
           <cell r="B519" t="str">
-            <v>个人意识</v>
+            <v>稀有盾牌</v>
           </cell>
           <cell r="C519">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="520">
           <cell r="A520">
-            <v>902078</v>
+            <v>902045</v>
           </cell>
           <cell r="B520" t="str">
-            <v>灵感</v>
+            <v>特殊盾牌</v>
           </cell>
           <cell r="C520">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="521">
           <cell r="A521">
-            <v>902080</v>
+            <v>902048</v>
           </cell>
           <cell r="B521" t="str">
-            <v>勇气</v>
+            <v>极品盾牌</v>
           </cell>
           <cell r="C521">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="522">
           <cell r="A522">
-            <v>902081</v>
+            <v>902070</v>
           </cell>
           <cell r="B522" t="str">
-            <v>自由恋爱</v>
+            <v>传说盾牌</v>
           </cell>
           <cell r="C522">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="523">
           <cell r="A523">
-            <v>902082</v>
+            <v>902073</v>
           </cell>
           <cell r="B523" t="str">
-            <v>惩罚制度</v>
+            <v>史诗盾牌</v>
           </cell>
           <cell r="C523">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="524">
           <cell r="A524">
-            <v>902083</v>
+            <v>902052</v>
           </cell>
           <cell r="B524" t="str">
-            <v>奖励制度</v>
+            <v>锻造</v>
           </cell>
           <cell r="C524">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="525">
           <cell r="A525">
-            <v>902084</v>
+            <v>902053</v>
           </cell>
           <cell r="B525" t="str">
-            <v>怪物驯化</v>
+            <v>弓矢</v>
           </cell>
           <cell r="C525">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="526">
           <cell r="A526">
-            <v>902085</v>
+            <v>902054</v>
           </cell>
           <cell r="B526" t="str">
-            <v>农夫雕像</v>
+            <v>弩机</v>
           </cell>
           <cell r="C526">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="527">
           <cell r="A527">
-            <v>902086</v>
+            <v>902055</v>
           </cell>
           <cell r="B527" t="str">
-            <v>精灵雕像</v>
+            <v>盾牌</v>
           </cell>
           <cell r="C527">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="528">
           <cell r="A528">
-            <v>902087</v>
+            <v>902056</v>
           </cell>
           <cell r="B528" t="str">
-            <v>士兵雕像</v>
+            <v>巨盾</v>
           </cell>
           <cell r="C528">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="529">
           <cell r="A529">
-            <v>902088</v>
+            <v>902057</v>
           </cell>
           <cell r="B529" t="str">
-            <v>渔夫雕像</v>
+            <v>骑射</v>
           </cell>
           <cell r="C529">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="530">
           <cell r="A530">
-            <v>902089</v>
+            <v>902059</v>
           </cell>
           <cell r="B530" t="str">
-            <v>牧民雕像</v>
+            <v>人伦书</v>
           </cell>
           <cell r="C530">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="531">
           <cell r="A531">
-            <v>902090</v>
+            <v>902060</v>
           </cell>
           <cell r="B531" t="str">
-            <v>城墙</v>
+            <v>轮回书</v>
           </cell>
           <cell r="C531">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="532">
           <cell r="A532">
-            <v>902091</v>
+            <v>902061</v>
           </cell>
           <cell r="B532" t="str">
-            <v>开山采石</v>
+            <v>货架</v>
           </cell>
           <cell r="C532">
-            <v>500</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="533">
           <cell r="A533">
-            <v>902092</v>
+            <v>902063</v>
           </cell>
           <cell r="B533" t="str">
-            <v>大炮</v>
+            <v>填水造陆</v>
           </cell>
           <cell r="C533">
-            <v>500</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="534">
           <cell r="A534">
-            <v>902093</v>
+            <v>902064</v>
           </cell>
           <cell r="B534" t="str">
-            <v>战舰</v>
+            <v>开挖河道</v>
           </cell>
           <cell r="C534">
-            <v>500</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="535">
           <cell r="A535">
-            <v>902094</v>
+            <v>902065</v>
           </cell>
           <cell r="B535" t="str">
-            <v>航海术</v>
+            <v>边境贸易</v>
           </cell>
           <cell r="C535">
-            <v>500</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="536">
           <cell r="A536">
-            <v>902095</v>
+            <v>902066</v>
           </cell>
           <cell r="B536" t="str">
-            <v>巨型战舰</v>
+            <v>马车运输</v>
           </cell>
           <cell r="C536">
-            <v>500</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="537">
           <cell r="A537">
-            <v>902096</v>
+            <v>902074</v>
           </cell>
           <cell r="B537" t="str">
-            <v>方尖碑</v>
+            <v>牢房</v>
           </cell>
           <cell r="C537">
-            <v>500</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="538">
           <cell r="A538">
-            <v>902097</v>
+            <v>902075</v>
           </cell>
           <cell r="B538" t="str">
-            <v>铁弹</v>
+            <v>壁炉</v>
           </cell>
           <cell r="C538">
             <v>500</v>
@@ -6979,10 +7055,10 @@
         </row>
         <row r="539">
           <cell r="A539">
-            <v>902098</v>
+            <v>902077</v>
           </cell>
           <cell r="B539" t="str">
-            <v>弹道</v>
+            <v>个人意识</v>
           </cell>
           <cell r="C539">
             <v>500</v>
@@ -6990,10 +7066,10 @@
         </row>
         <row r="540">
           <cell r="A540">
-            <v>902099</v>
+            <v>902078</v>
           </cell>
           <cell r="B540" t="str">
-            <v>旅店</v>
+            <v>灵感</v>
           </cell>
           <cell r="C540">
             <v>500</v>
@@ -7001,10 +7077,10 @@
         </row>
         <row r="541">
           <cell r="A541">
-            <v>902100</v>
+            <v>902080</v>
           </cell>
           <cell r="B541" t="str">
-            <v>巨型炸弹</v>
+            <v>勇气</v>
           </cell>
           <cell r="C541">
             <v>500</v>
@@ -7012,10 +7088,10 @@
         </row>
         <row r="542">
           <cell r="A542">
-            <v>902101</v>
+            <v>902081</v>
           </cell>
           <cell r="B542" t="str">
-            <v>泰坦祭坛</v>
+            <v>自由恋爱</v>
           </cell>
           <cell r="C542">
             <v>500</v>
@@ -7023,10 +7099,10 @@
         </row>
         <row r="543">
           <cell r="A543">
-            <v>902102</v>
+            <v>902082</v>
           </cell>
           <cell r="B543" t="str">
-            <v>深井开采</v>
+            <v>惩罚制度</v>
           </cell>
           <cell r="C543">
             <v>500</v>
@@ -7034,10 +7110,10 @@
         </row>
         <row r="544">
           <cell r="A544">
-            <v>902103</v>
+            <v>902083</v>
           </cell>
           <cell r="B544" t="str">
-            <v>法杖</v>
+            <v>奖励制度</v>
           </cell>
           <cell r="C544">
             <v>500</v>
@@ -7045,10 +7121,10 @@
         </row>
         <row r="545">
           <cell r="A545">
-            <v>902104</v>
+            <v>902084</v>
           </cell>
           <cell r="B545" t="str">
-            <v>地下穴居</v>
+            <v>怪物驯化</v>
           </cell>
           <cell r="C545">
             <v>500</v>
@@ -7056,65 +7132,65 @@
         </row>
         <row r="546">
           <cell r="A546">
-            <v>902105</v>
+            <v>902085</v>
           </cell>
           <cell r="B546" t="str">
-            <v>传送门</v>
+            <v>农夫雕像</v>
           </cell>
           <cell r="C546">
-            <v>500</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="547">
           <cell r="A547">
-            <v>902106</v>
+            <v>902086</v>
           </cell>
           <cell r="B547" t="str">
-            <v>节日庆典</v>
+            <v>精灵雕像</v>
           </cell>
           <cell r="C547">
-            <v>500</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="548">
           <cell r="A548">
-            <v>902108</v>
+            <v>902087</v>
           </cell>
           <cell r="B548" t="str">
-            <v>钩爪</v>
+            <v>士兵雕像</v>
           </cell>
           <cell r="C548">
-            <v>500</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="549">
           <cell r="A549">
-            <v>902109</v>
+            <v>902088</v>
           </cell>
           <cell r="B549" t="str">
-            <v>成片施肥</v>
+            <v>渔夫雕像</v>
           </cell>
           <cell r="C549">
-            <v>500</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="550">
           <cell r="A550">
-            <v>902110</v>
+            <v>902089</v>
           </cell>
           <cell r="B550" t="str">
-            <v>尚武精神</v>
+            <v>牧民雕像</v>
           </cell>
           <cell r="C550">
-            <v>500</v>
+            <v>100000</v>
           </cell>
         </row>
         <row r="551">
           <cell r="A551">
-            <v>902111</v>
+            <v>902090</v>
           </cell>
           <cell r="B551" t="str">
-            <v>人口政策</v>
+            <v>城墙</v>
           </cell>
           <cell r="C551">
             <v>500</v>
@@ -7122,10 +7198,10 @@
         </row>
         <row r="552">
           <cell r="A552">
-            <v>902112</v>
+            <v>902091</v>
           </cell>
           <cell r="B552" t="str">
-            <v>启蒙书</v>
+            <v>开山采石</v>
           </cell>
           <cell r="C552">
             <v>500</v>
@@ -7133,10 +7209,10 @@
         </row>
         <row r="553">
           <cell r="A553">
-            <v>902113</v>
+            <v>902092</v>
           </cell>
           <cell r="B553" t="str">
-            <v>磨坊</v>
+            <v>大炮</v>
           </cell>
           <cell r="C553">
             <v>500</v>
@@ -7144,10 +7220,10 @@
         </row>
         <row r="554">
           <cell r="A554">
-            <v>902114</v>
+            <v>902093</v>
           </cell>
           <cell r="B554" t="str">
-            <v>心灵书</v>
+            <v>战舰</v>
           </cell>
           <cell r="C554">
             <v>500</v>
@@ -7155,10 +7231,10 @@
         </row>
         <row r="555">
           <cell r="A555">
-            <v>902115</v>
+            <v>902094</v>
           </cell>
           <cell r="B555" t="str">
-            <v>野营</v>
+            <v>航海术</v>
           </cell>
           <cell r="C555">
             <v>500</v>
@@ -7166,10 +7242,10 @@
         </row>
         <row r="556">
           <cell r="A556">
-            <v>902116</v>
+            <v>902095</v>
           </cell>
           <cell r="B556" t="str">
-            <v>蘑菇培育</v>
+            <v>巨型战舰</v>
           </cell>
           <cell r="C556">
             <v>500</v>
@@ -7177,10 +7253,10 @@
         </row>
         <row r="557">
           <cell r="A557">
-            <v>902117</v>
+            <v>902096</v>
           </cell>
           <cell r="B557" t="str">
-            <v>倾听</v>
+            <v>方尖碑</v>
           </cell>
           <cell r="C557">
             <v>500</v>
@@ -7188,10 +7264,10 @@
         </row>
         <row r="558">
           <cell r="A558">
-            <v>902118</v>
+            <v>902097</v>
           </cell>
           <cell r="B558" t="str">
-            <v>光明祭坛</v>
+            <v>铁弹</v>
           </cell>
           <cell r="C558">
             <v>500</v>
@@ -7199,10 +7275,10 @@
         </row>
         <row r="559">
           <cell r="A559">
-            <v>902119</v>
+            <v>902098</v>
           </cell>
           <cell r="B559" t="str">
-            <v>黑暗祭坛</v>
+            <v>弹道</v>
           </cell>
           <cell r="C559">
             <v>500</v>
@@ -7210,230 +7286,230 @@
         </row>
         <row r="560">
           <cell r="A560">
-            <v>902120</v>
+            <v>902099</v>
           </cell>
           <cell r="B560" t="str">
-            <v>天职书</v>
+            <v>旅店</v>
           </cell>
           <cell r="C560">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="561">
           <cell r="A561">
-            <v>902122</v>
+            <v>902100</v>
           </cell>
           <cell r="B561" t="str">
-            <v>冰窖</v>
+            <v>巨型炸弹</v>
           </cell>
           <cell r="C561">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="562">
           <cell r="A562">
-            <v>902123</v>
+            <v>902101</v>
           </cell>
           <cell r="B562" t="str">
-            <v>地雷</v>
+            <v>泰坦祭坛</v>
           </cell>
           <cell r="C562">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="563">
           <cell r="A563">
-            <v>902124</v>
+            <v>902102</v>
           </cell>
           <cell r="B563" t="str">
-            <v>强制劳动</v>
+            <v>深井开采</v>
           </cell>
           <cell r="C563">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="564">
           <cell r="A564">
-            <v>902125</v>
+            <v>902103</v>
           </cell>
           <cell r="B564" t="str">
-            <v>官员选拔</v>
+            <v>法杖</v>
           </cell>
           <cell r="C564">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="565">
           <cell r="A565">
-            <v>902126</v>
+            <v>902104</v>
           </cell>
           <cell r="B565" t="str">
-            <v>政治联姻</v>
+            <v>地下穴居</v>
           </cell>
           <cell r="C565">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="566">
           <cell r="A566">
-            <v>902127</v>
+            <v>902105</v>
           </cell>
           <cell r="B566" t="str">
-            <v>火枪</v>
+            <v>传送门</v>
           </cell>
           <cell r="C566">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="567">
           <cell r="A567">
-            <v>902128</v>
+            <v>902106</v>
           </cell>
           <cell r="B567" t="str">
-            <v>驯狼</v>
+            <v>节日庆典</v>
           </cell>
           <cell r="C567">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="568">
           <cell r="A568">
-            <v>902129</v>
+            <v>902108</v>
           </cell>
           <cell r="B568" t="str">
-            <v>水晶球</v>
+            <v>钩爪</v>
           </cell>
           <cell r="C568">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="569">
           <cell r="A569">
-            <v>902130</v>
+            <v>902109</v>
           </cell>
           <cell r="B569" t="str">
-            <v>冶炼</v>
+            <v>成片施肥</v>
           </cell>
           <cell r="C569">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="570">
           <cell r="A570">
-            <v>902131</v>
+            <v>902110</v>
           </cell>
           <cell r="B570" t="str">
-            <v>高级冶炼</v>
+            <v>尚武精神</v>
           </cell>
           <cell r="C570">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="571">
           <cell r="A571">
-            <v>902132</v>
+            <v>902111</v>
           </cell>
           <cell r="B571" t="str">
-            <v>奇观</v>
+            <v>人口政策</v>
           </cell>
           <cell r="C571">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="572">
           <cell r="A572">
-            <v>902133</v>
+            <v>902112</v>
           </cell>
           <cell r="B572" t="str">
-            <v>王座</v>
+            <v>启蒙书</v>
           </cell>
           <cell r="C572">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="573">
           <cell r="A573">
-            <v>902134</v>
+            <v>902113</v>
           </cell>
           <cell r="B573" t="str">
-            <v>社会抚养</v>
+            <v>磨坊</v>
           </cell>
           <cell r="C573">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="574">
           <cell r="A574">
-            <v>902135</v>
+            <v>902114</v>
           </cell>
           <cell r="B574" t="str">
-            <v>地板</v>
+            <v>心灵书</v>
           </cell>
           <cell r="C574">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="575">
           <cell r="A575">
-            <v>902136</v>
+            <v>902115</v>
           </cell>
           <cell r="B575" t="str">
-            <v>石质地板</v>
+            <v>野营</v>
           </cell>
           <cell r="C575">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="576">
           <cell r="A576">
-            <v>902137</v>
+            <v>902116</v>
           </cell>
           <cell r="B576" t="str">
-            <v>铁质地板</v>
+            <v>蘑菇培育</v>
           </cell>
           <cell r="C576">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="577">
           <cell r="A577">
-            <v>902138</v>
+            <v>902117</v>
           </cell>
           <cell r="B577" t="str">
-            <v>银质地板</v>
+            <v>倾诉</v>
           </cell>
           <cell r="C577">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="578">
           <cell r="A578">
-            <v>902139</v>
+            <v>902118</v>
           </cell>
           <cell r="B578" t="str">
-            <v>金质地板</v>
+            <v>光明祭坛</v>
           </cell>
           <cell r="C578">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="579">
           <cell r="A579">
-            <v>902140</v>
+            <v>902119</v>
           </cell>
           <cell r="B579" t="str">
-            <v>博彩</v>
+            <v>黑暗祭坛</v>
           </cell>
           <cell r="C579">
-            <v>2000</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="580">
           <cell r="A580">
-            <v>902141</v>
+            <v>902120</v>
           </cell>
           <cell r="B580" t="str">
-            <v>公共浴场</v>
+            <v>天职书</v>
           </cell>
           <cell r="C580">
             <v>2000</v>
@@ -7441,10 +7517,10 @@
         </row>
         <row r="581">
           <cell r="A581">
-            <v>902142</v>
+            <v>902122</v>
           </cell>
           <cell r="B581" t="str">
-            <v>军事训练</v>
+            <v>冰窖</v>
           </cell>
           <cell r="C581">
             <v>2000</v>
@@ -7452,10 +7528,10 @@
         </row>
         <row r="582">
           <cell r="A582">
-            <v>902143</v>
+            <v>902123</v>
           </cell>
           <cell r="B582" t="str">
-            <v>铁墙</v>
+            <v>地雷</v>
           </cell>
           <cell r="C582">
             <v>2000</v>
@@ -7463,10 +7539,10 @@
         </row>
         <row r="583">
           <cell r="A583">
-            <v>902144</v>
+            <v>902124</v>
           </cell>
           <cell r="B583" t="str">
-            <v>国库</v>
+            <v>强制劳动</v>
           </cell>
           <cell r="C583">
             <v>2000</v>
@@ -7474,21 +7550,21 @@
         </row>
         <row r="584">
           <cell r="A584">
-            <v>902145</v>
+            <v>902125</v>
           </cell>
           <cell r="B584" t="str">
-            <v>BUG雕像</v>
+            <v>官员选拔</v>
           </cell>
           <cell r="C584">
-            <v>10000</v>
+            <v>2000</v>
           </cell>
         </row>
         <row r="585">
           <cell r="A585">
-            <v>902146</v>
+            <v>902126</v>
           </cell>
           <cell r="B585" t="str">
-            <v>继承人选拔</v>
+            <v>政治联姻</v>
           </cell>
           <cell r="C585">
             <v>2000</v>
@@ -7496,10 +7572,10 @@
         </row>
         <row r="586">
           <cell r="A586">
-            <v>902147</v>
+            <v>902127</v>
           </cell>
           <cell r="B586" t="str">
-            <v>兽药</v>
+            <v>火枪</v>
           </cell>
           <cell r="C586">
             <v>2000</v>
@@ -7507,10 +7583,10 @@
         </row>
         <row r="587">
           <cell r="A587">
-            <v>902148</v>
+            <v>902128</v>
           </cell>
           <cell r="B587" t="str">
-            <v>永恒圣殿</v>
+            <v>驯狼</v>
           </cell>
           <cell r="C587">
             <v>2000</v>
@@ -7518,10 +7594,10 @@
         </row>
         <row r="588">
           <cell r="A588">
-            <v>902149</v>
+            <v>902129</v>
           </cell>
           <cell r="B588" t="str">
-            <v>兵法书</v>
+            <v>水晶球</v>
           </cell>
           <cell r="C588">
             <v>2000</v>
@@ -7529,10 +7605,10 @@
         </row>
         <row r="589">
           <cell r="A589">
-            <v>902150</v>
+            <v>902130</v>
           </cell>
           <cell r="B589" t="str">
-            <v>管理书</v>
+            <v>冶炼</v>
           </cell>
           <cell r="C589">
             <v>2000</v>
@@ -7540,10 +7616,10 @@
         </row>
         <row r="590">
           <cell r="A590">
-            <v>902151</v>
+            <v>902131</v>
           </cell>
           <cell r="B590" t="str">
-            <v>忠义书</v>
+            <v>高级冶炼</v>
           </cell>
           <cell r="C590">
             <v>2000</v>
@@ -7551,10 +7627,10 @@
         </row>
         <row r="591">
           <cell r="A591">
-            <v>902152</v>
+            <v>902132</v>
           </cell>
           <cell r="B591" t="str">
-            <v>高效收纳</v>
+            <v>奇观</v>
           </cell>
           <cell r="C591">
             <v>2000</v>
@@ -7562,10 +7638,10 @@
         </row>
         <row r="592">
           <cell r="A592">
-            <v>902153</v>
+            <v>902133</v>
           </cell>
           <cell r="B592" t="str">
-            <v>熏肉</v>
+            <v>王座</v>
           </cell>
           <cell r="C592">
             <v>2000</v>
@@ -7573,10 +7649,10 @@
         </row>
         <row r="593">
           <cell r="A593">
-            <v>902154</v>
+            <v>902134</v>
           </cell>
           <cell r="B593" t="str">
-            <v>糕点</v>
+            <v>社会抚养</v>
           </cell>
           <cell r="C593">
             <v>2000</v>
@@ -7584,17 +7660,326 @@
         </row>
         <row r="594">
           <cell r="A594">
-            <v>902155</v>
+            <v>902135</v>
           </cell>
           <cell r="B594" t="str">
-            <v>零食</v>
+            <v>地板</v>
           </cell>
           <cell r="C594">
             <v>2000</v>
           </cell>
         </row>
+        <row r="595">
+          <cell r="A595">
+            <v>902136</v>
+          </cell>
+          <cell r="B595" t="str">
+            <v>石质地板</v>
+          </cell>
+          <cell r="C595">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="596">
+          <cell r="A596">
+            <v>902137</v>
+          </cell>
+          <cell r="B596" t="str">
+            <v>铁质地板</v>
+          </cell>
+          <cell r="C596">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="597">
+          <cell r="A597">
+            <v>902138</v>
+          </cell>
+          <cell r="B597" t="str">
+            <v>银质地板</v>
+          </cell>
+          <cell r="C597">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="598">
+          <cell r="A598">
+            <v>902139</v>
+          </cell>
+          <cell r="B598" t="str">
+            <v>金质地板</v>
+          </cell>
+          <cell r="C598">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="599">
+          <cell r="A599">
+            <v>902140</v>
+          </cell>
+          <cell r="B599" t="str">
+            <v>博彩</v>
+          </cell>
+          <cell r="C599">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="600">
+          <cell r="A600">
+            <v>902141</v>
+          </cell>
+          <cell r="B600" t="str">
+            <v>公共浴场</v>
+          </cell>
+          <cell r="C600">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="601">
+          <cell r="A601">
+            <v>902142</v>
+          </cell>
+          <cell r="B601" t="str">
+            <v>军事训练</v>
+          </cell>
+          <cell r="C601">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="602">
+          <cell r="A602">
+            <v>902143</v>
+          </cell>
+          <cell r="B602" t="str">
+            <v>铁墙</v>
+          </cell>
+          <cell r="C602">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="603">
+          <cell r="A603">
+            <v>902144</v>
+          </cell>
+          <cell r="B603" t="str">
+            <v>国库</v>
+          </cell>
+          <cell r="C603">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="604">
+          <cell r="A604">
+            <v>902145</v>
+          </cell>
+          <cell r="B604" t="str">
+            <v>BUG雕像</v>
+          </cell>
+          <cell r="C604">
+            <v>100000</v>
+          </cell>
+        </row>
+        <row r="605">
+          <cell r="A605">
+            <v>902146</v>
+          </cell>
+          <cell r="B605" t="str">
+            <v>继承人选拔</v>
+          </cell>
+          <cell r="C605">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="606">
+          <cell r="A606">
+            <v>902147</v>
+          </cell>
+          <cell r="B606" t="str">
+            <v>兽药</v>
+          </cell>
+          <cell r="C606">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="607">
+          <cell r="A607">
+            <v>902148</v>
+          </cell>
+          <cell r="B607" t="str">
+            <v>永恒圣殿</v>
+          </cell>
+          <cell r="C607">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="608">
+          <cell r="A608">
+            <v>902149</v>
+          </cell>
+          <cell r="B608" t="str">
+            <v>兵法书</v>
+          </cell>
+          <cell r="C608">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="609">
+          <cell r="A609">
+            <v>902150</v>
+          </cell>
+          <cell r="B609" t="str">
+            <v>管理书</v>
+          </cell>
+          <cell r="C609">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="610">
+          <cell r="A610">
+            <v>902151</v>
+          </cell>
+          <cell r="B610" t="str">
+            <v>忠义书</v>
+          </cell>
+          <cell r="C610">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="611">
+          <cell r="A611">
+            <v>902152</v>
+          </cell>
+          <cell r="B611" t="str">
+            <v>高效收纳</v>
+          </cell>
+          <cell r="C611">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="612">
+          <cell r="A612">
+            <v>902153</v>
+          </cell>
+          <cell r="B612" t="str">
+            <v>熏肉</v>
+          </cell>
+          <cell r="C612">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="613">
+          <cell r="A613">
+            <v>902154</v>
+          </cell>
+          <cell r="B613" t="str">
+            <v>糕点</v>
+          </cell>
+          <cell r="C613">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="614">
+          <cell r="A614">
+            <v>902155</v>
+          </cell>
+          <cell r="B614" t="str">
+            <v>零食</v>
+          </cell>
+          <cell r="C614">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="615">
+          <cell r="A615">
+            <v>902156</v>
+          </cell>
+          <cell r="B615" t="str">
+            <v>药茶</v>
+          </cell>
+          <cell r="C615">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="616">
+          <cell r="A616">
+            <v>902157</v>
+          </cell>
+          <cell r="B616" t="str">
+            <v>糖</v>
+          </cell>
+          <cell r="C616">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="617">
+          <cell r="A617">
+            <v>902158</v>
+          </cell>
+          <cell r="B617" t="str">
+            <v>蘑菇精华</v>
+          </cell>
+          <cell r="C617">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="618">
+          <cell r="A618">
+            <v>902159</v>
+          </cell>
+          <cell r="B618" t="str">
+            <v>养颜丹</v>
+          </cell>
+          <cell r="C618">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="619">
+          <cell r="A619">
+            <v>902160</v>
+          </cell>
+          <cell r="B619" t="str">
+            <v>果园</v>
+          </cell>
+          <cell r="C619">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="620">
+          <cell r="A620">
+            <v>902161</v>
+          </cell>
+          <cell r="B620" t="str">
+            <v>百科全书</v>
+          </cell>
+          <cell r="C620">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="621">
+          <cell r="A621">
+            <v>902162</v>
+          </cell>
+          <cell r="B621" t="str">
+            <v>鲜花雕像</v>
+          </cell>
+          <cell r="C621">
+            <v>100000</v>
+          </cell>
+        </row>
+        <row r="622">
+          <cell r="A622">
+            <v>902163</v>
+          </cell>
+          <cell r="B622" t="str">
+            <v>萨满教思想</v>
+          </cell>
+          <cell r="C622">
+            <v>2000</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7887,7 +8272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CC12"/>
+  <dimension ref="A1:CF12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -7910,7 +8295,7 @@
     <col min="81" max="81" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" ht="81" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:84" ht="81" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -8150,8 +8535,17 @@
       <c r="CC1" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="CD1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="CE1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="CF1" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
-    <row r="2" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -8395,8 +8789,17 @@
       <c r="CC2" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="CD2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CE2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
-    <row r="3" spans="1:81" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:84" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>501001</v>
       </c>
@@ -8646,8 +9049,17 @@
       <c r="CC3" s="1">
         <v>45</v>
       </c>
+      <c r="CD3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="CF3" s="2">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:81" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:84" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>501002</v>
       </c>
@@ -8904,8 +9316,17 @@
       <c r="CC4" s="1">
         <v>30</v>
       </c>
+      <c r="CD4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="CE4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="CF4" s="2">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:81" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:84" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>501003</v>
       </c>
@@ -9157,8 +9578,17 @@
       <c r="CC5" s="1">
         <v>30</v>
       </c>
+      <c r="CD5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="CE5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="CF5" s="2">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>501004</v>
       </c>
@@ -9409,8 +9839,17 @@
       <c r="CC6" s="1">
         <v>30</v>
       </c>
+      <c r="CD6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="CE6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="CF6" s="2">
+        <v>19</v>
+      </c>
     </row>
-    <row r="7" spans="1:81" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:84" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>501005</v>
       </c>
@@ -9661,8 +10100,17 @@
       <c r="CC7" s="1">
         <v>60</v>
       </c>
+      <c r="CD7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="CE7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="CF7" s="2">
+        <v>19</v>
+      </c>
     </row>
-    <row r="8" spans="1:81" ht="54" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:84" ht="54" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>501006</v>
       </c>
@@ -9913,8 +10361,17 @@
       <c r="CC8" s="1">
         <v>30</v>
       </c>
+      <c r="CD8" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="CE8" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="CF8" s="2">
+        <v>19</v>
+      </c>
     </row>
-    <row r="9" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>502001</v>
       </c>
@@ -10157,8 +10614,17 @@
       <c r="CC9" s="1">
         <v>30</v>
       </c>
+      <c r="CD9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="CE9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="CF9" s="2">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>805001</v>
       </c>
@@ -10388,8 +10854,13 @@
       <c r="CC10" s="1">
         <v>0</v>
       </c>
+      <c r="CD10" s="1"/>
+      <c r="CE10" s="1"/>
+      <c r="CF10" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>502005</v>
       </c>
@@ -10632,8 +11103,17 @@
       <c r="CC11" s="1">
         <v>30</v>
       </c>
+      <c r="CD11" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="CE11" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="CF11" s="2">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>502006</v>
       </c>
@@ -10876,11 +11356,20 @@
       <c r="CC12" s="1">
         <v>30</v>
       </c>
+      <c r="CD12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="CE12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="CF12" s="2">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="BY1:BZ2 CA1:CC1">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="BY1:BZ2 CA1:CF1">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
